--- a/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{667BFE88-3BB0-4DBF-80F2-31641C1ADE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2565F68D-E3AA-4131-BB95-0802A571851E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{42CDF774-8265-41B8-9491-177C84AFDBBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA2D2DF-F680-4A22-A86A-98340D92839F}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="162">
   <si>
     <t>通番</t>
   </si>
@@ -123,7 +123,7 @@
     <t>操作</t>
   </si>
   <si>
-    <t>期待結果</t>
+    <t>期待値</t>
   </si>
   <si>
     <t>参照</t>
@@ -135,7 +135,14 @@
     <t>正常系</t>
   </si>
   <si>
-    <t>対象のグループ：ok、処理のチェック：初期状態（5 件オン、2 件オフ）</t>
+    <t>対象のグループ：ok
+実施結果取得-テスト：あり
+実施結果取得-アンケート：あり
+実施状況確認-テスト・アンケート：あり
+実施結果集計-テスト：あり
+実施結果集計-アンケート：あり
+実施結果集計-投稿：なし
+経年比較-アンケート・テスト：なし</t>
   </si>
   <si>
     <t>実行を押します。</t>
@@ -144,19 +151,23 @@
     <t>処理ごとの状態：成功または警告</t>
   </si>
   <si>
-    <t>画面設計 3.1、処理フロー 2.1</t>
+    <t>画面設計：3.1
+処理フロー：2.1</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>対象のグループ：ok、実施結果取得-テストのチェック：なし</t>
-  </si>
-  <si>
-    <t>実施結果取得-テストの状態：（空）、ほかの処理：実行される</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、実施結果集計-投稿のチェック：あり</t>
+    <t>対象のグループ：ok
+実施結果取得-テスト：なし</t>
+  </si>
+  <si>
+    <t>実施結果取得-テストの状態：（空）
+ほかの処理：実行される</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+実施結果集計-投稿：あり</t>
   </si>
   <si>
     <t>実施結果集計-投稿の状態：成功または警告</t>
@@ -174,7 +185,8 @@
     <t>実行が終わったあと、ログ欄を確認します。</t>
   </si>
   <si>
-    <t>画面下部のログ：実行の結果、ログの出力先：実行ログ</t>
+    <t>画面下部のログ：実行の結果
+ログの出力先：実行ログ</t>
   </si>
   <si>
     <t>すべての行の「開く」を押します。</t>
@@ -183,7 +195,7 @@
     <t>開いた画面：処理の結果のフォルダ、または投稿先のスレッド</t>
   </si>
   <si>
-    <t>画面設計 3.1</t>
+    <t>画面設計：3.1</t>
   </si>
   <si>
     <t>異常系</t>
@@ -192,13 +204,16 @@
     <t>対象のグループ：ng</t>
   </si>
   <si>
-    <t>実施結果取得-テストの状態：失敗、後続の処理：実行される</t>
-  </si>
-  <si>
-    <t>状態：成功または警告、取得結果：テストの実施結果</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.2</t>
+    <t>実施結果取得-テストの状態：失敗
+後続の処理：実行される</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+取得結果：テストの実施結果</t>
+  </si>
+  <si>
+    <t>画面設計：3.2
+処理フロー：2.2</t>
   </si>
   <si>
     <t>実行が終わったあと、開くを押します。</t>
@@ -207,94 +222,111 @@
     <t>開いた画面：取得した結果のフォルダ</t>
   </si>
   <si>
-    <t>画面設計 3.2</t>
-  </si>
-  <si>
-    <t>状態：成功または警告、取得結果：アンケートの実施結果</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.3</t>
+    <t>画面設計：3.2</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+取得結果：アンケートの実施結果</t>
+  </si>
+  <si>
+    <t>画面設計：3.2
+処理フロー：2.3</t>
   </si>
   <si>
     <t>状態：成功または警告</t>
   </si>
   <si>
-    <t>画面設計 3.2、処理フロー 2.4</t>
+    <t>画面設計：3.2
+処理フロー：2.4</t>
   </si>
   <si>
     <t>テストの実行を押します。</t>
   </si>
   <si>
-    <t>状態：失敗、取得結果：なし</t>
+    <t>状態：失敗
+取得結果：なし</t>
   </si>
   <si>
     <t>アンケートの実行を押します。</t>
   </si>
   <si>
-    <t>状態：成功または警告、統合結果：取得した結果</t>
-  </si>
-  <si>
-    <t>画面設計 3.3、処理フロー 2.5</t>
+    <t>状態：成功または警告
+統合結果：取得した結果</t>
+  </si>
+  <si>
+    <t>画面設計：3.3
+処理フロー：2.5</t>
   </si>
   <si>
     <t>開いた画面：統合結果のフォルダ</t>
   </si>
   <si>
-    <t>画面設計 3.3</t>
-  </si>
-  <si>
-    <t>状態：成功または警告、集計結果：テストの集計結果</t>
-  </si>
-  <si>
-    <t>画面設計 3.4、処理フロー 2.6</t>
+    <t>画面設計：3.3</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+集計結果：テストの集計結果</t>
+  </si>
+  <si>
+    <t>画面設計：3.4
+処理フロー：2.6</t>
   </si>
   <si>
     <t>開いた画面：テスト集計結果のフォルダ</t>
   </si>
   <si>
-    <t>画面設計 3.4</t>
-  </si>
-  <si>
-    <t>状態：成功または警告、集計結果：アンケートの集計結果</t>
-  </si>
-  <si>
-    <t>画面設計 3.4、処理フロー 2.7</t>
+    <t>画面設計：3.4</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+集計結果：アンケートの集計結果</t>
+  </si>
+  <si>
+    <t>画面設計：3.4
+処理フロー：2.7</t>
   </si>
   <si>
     <t>開いた画面：アンケート集計結果のフォルダ</t>
   </si>
   <si>
-    <t>状態：成功または警告、投稿：集計結果が投稿先のスレッドに投稿される</t>
-  </si>
-  <si>
-    <t>画面設計 3.4、処理フロー 2.8</t>
+    <t>状態：成功または警告
+投稿：集計結果が投稿先のスレッドに投稿される</t>
+  </si>
+  <si>
+    <t>画面設計：3.4
+処理フロー：2.8</t>
   </si>
   <si>
     <t>開いた画面：投稿先のスレッド（ブラウザ）</t>
   </si>
   <si>
-    <t>対象のグループ：ok、対象の会社名：空</t>
-  </si>
-  <si>
-    <t>状態：成功または警告、経年比較の結果：作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.5、処理フロー 2.9</t>
+    <t>対象のグループ：ok
+対象の会社名：空</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+経年比較の結果：作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.5
+処理フロー：2.9</t>
   </si>
   <si>
     <t>開いた画面：経年比較の結果のフォルダ</t>
   </si>
   <si>
-    <t>画面設計 3.5</t>
+    <t>画面設計：3.5</t>
   </si>
   <si>
     <t>ログのファイルがない状態で、すべて削除を押します。</t>
   </si>
   <si>
-    <t>メッセージ：「削除対象のログファイルがありません。」、処理：終わる</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.10</t>
+    <t>メッセージ：「削除対象のログファイルがありません。」
+処理：終わる</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.10</t>
   </si>
   <si>
     <t>確認：いいえ</t>
@@ -303,7 +335,8 @@
     <t>ログのファイルがある状態で、すべて削除を押します。</t>
   </si>
   <si>
-    <t>削除：なし、ログのファイル：残る</t>
+    <t>削除：なし
+ログのファイル：残る</t>
   </si>
   <si>
     <t>確認：はい</t>
@@ -312,46 +345,50 @@
     <t>ログのファイル：すべて削除される</t>
   </si>
   <si>
-    <t>対象のグループ：すべて、ok</t>
+    <t>対象のグループ：すべて、ok、ng</t>
   </si>
   <si>
     <t>対象のグループを選びます。</t>
   </si>
   <si>
-    <t>表示されるログ：「すべて」を選ぶと両方、「ok」を選ぶと ok のログだけ</t>
-  </si>
-  <si>
-    <t>画面設計 3.6</t>
+    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
+  </si>
+  <si>
+    <t>画面設計：3.6</t>
   </si>
   <si>
     <t>処理のラジオボタンを切り替えます。</t>
   </si>
   <si>
-    <t>表示されるログ：選んだ処理のログだけ</t>
-  </si>
-  <si>
-    <t>テスト結果ファイル名の接尾語：suffix-test</t>
+    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
+  </si>
+  <si>
+    <t>テスト結果ファイル名の接尾語：saved</t>
   </si>
   <si>
     <t>保存を押します。</t>
   </si>
   <si>
-    <t>保存先：bats\common.bat、画面の表示：保存後の内容に更新</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.11</t>
-  </si>
-  <si>
-    <t>テスト結果ファイル名の接尾語：suffix-tmp</t>
+    <t>保存先：bats\common.bat
+画面の表示：保存後の内容に更新</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.11</t>
+  </si>
+  <si>
+    <t>テスト結果ファイル名の接尾語：tmp</t>
   </si>
   <si>
     <t>再読込を押します。</t>
   </si>
   <si>
-    <t>入力欄：保存されている値、変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.12</t>
+    <t>入力欄：保存されている値
+変えた内容：消える</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.12</t>
   </si>
   <si>
     <t>新しい名前：TrackNew</t>
@@ -363,34 +400,43 @@
     <t>一覧：新しい名前が追加され、選ばれる</t>
   </si>
   <si>
-    <t>画面設計 3.8、処理フロー 2.13</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、新しい名前：TrackCopy</t>
+    <t>画面設計：3.8
+処理フロー：2.13</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+新しい名前：TrackCopy</t>
   </si>
   <si>
     <t>保存済みのグループを選び、コピーを押します。</t>
   </si>
   <si>
-    <t>一覧：新しいグループが 1 つだけ追加され、選ばれる、設定ファイルと Excel ファイル：コピーされる</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.14</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、サブドメイン：track-saved</t>
-  </si>
-  <si>
-    <t>設定ファイル：値が保存される、画面の表示：保存後の内容に更新</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.15</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、サブドメイン：track-temp</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.16</t>
+    <t>一覧：新しいグループが 1 つだけ追加され、選ばれる
+設定ファイルと Excel ファイル：コピーされる</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.14</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：saved</t>
+  </si>
+  <si>
+    <t>設定ファイル：値が保存される
+画面の表示：保存後の内容に更新</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.15</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：tmp</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.16</t>
   </si>
   <si>
     <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
@@ -402,16 +448,19 @@
     <t>状態：成功</t>
   </si>
   <si>
-    <t>画面設計 3.8、処理フロー 2.17</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、対象アプリID：136</t>
+    <t>画面設計：3.8
+処理フロー：2.17</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID：136</t>
   </si>
   <si>
     <t>テスト接続（ユーザー）を押します。</t>
   </si>
   <si>
-    <t>画面設計 3.8、処理フロー 2.18</t>
+    <t>画面設計：3.8
+処理フロー：2.18</t>
   </si>
   <si>
     <t>対象のグループ：ok、入力なし（保存されている投稿先）</t>
@@ -420,16 +469,19 @@
     <t>テスト投稿を押します。</t>
   </si>
   <si>
-    <t>状態：成功、投稿：テスト用のコメント</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.19</t>
+    <t>状態：成功
+投稿：テスト用のコメント</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.19</t>
   </si>
   <si>
     <t>ok（既存のグループ名）</t>
   </si>
   <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」、一覧：追加されない</t>
+    <t>メッセージ：「（入力した名前）は既に存在します。」
+一覧：追加されない</t>
   </si>
   <si>
     <t>新規作成を押したあと、キャンセルを押します。</t>
@@ -441,25 +493,32 @@
     <t>10</t>
   </si>
   <si>
+    <t>新しい名前：TrackUnsaved</t>
+  </si>
+  <si>
     <t>新規作成直後の、まだ保存していないグループを選び、コピーを押します。</t>
   </si>
   <si>
-    <t>メッセージ：「コピー元のグループが存在しません。」、コピー：行われない</t>
+    <t>メッセージ：「コピー元のグループが存在しません。」
+コピー：行われない</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>対象のグループ：ok、サブドメイン：空</t>
-  </si>
-  <si>
-    <t>状態：失敗、接続：行われない</t>
+    <t>対象のグループ：ok
+サブドメイン：空</t>
+  </si>
+  <si>
+    <t>状態：失敗
+接続：行われない</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>対象のグループ：ok、パスワード：wrong-password</t>
+    <t>対象のグループ：ok
+パスワード：wrong-password</t>
   </si>
   <si>
     <t>状態：失敗</t>
@@ -468,13 +527,16 @@
     <t>13</t>
   </si>
   <si>
-    <t>対象のグループ：ok、対象アプリID：空</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、投稿先スペースID：空</t>
-  </si>
-  <si>
-    <t>状態：失敗、投稿：行われない</t>
+    <t>対象のグループ：ok
+対象アプリID：空</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スペースID：空</t>
+  </si>
+  <si>
+    <t>状態：失敗
+投稿：行われない</t>
   </si>
   <si>
     <t>テストの表で、追加（テスト）を押します。</t>
@@ -483,7 +545,8 @@
     <t>表：末尾に空の行が追加される</t>
   </si>
   <si>
-    <t>画面設計 3.9、処理フロー 2.24</t>
+    <t>画面設計：3.9
+処理フロー：2.24</t>
   </si>
   <si>
     <t>テストの表で、行を選んで削除（テスト）を押します。</t>
@@ -492,43 +555,53 @@
     <t>表：選んだ行が削除される</t>
   </si>
   <si>
-    <t>画面設計 3.9、処理フロー 2.23</t>
+    <t>画面設計：3.9
+処理フロー：2.23</t>
   </si>
   <si>
     <t>アンケートの表で、追加（アンケート）を押します。</t>
   </si>
   <si>
-    <t>画面設計 3.9、処理フロー 2.26</t>
+    <t>画面設計：3.9
+処理フロー：2.26</t>
   </si>
   <si>
     <t>アンケートの表で、行を選んで削除（アンケート）を押します。</t>
   </si>
   <si>
-    <t>画面設計 3.9、処理フロー 2.25</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、テスト名：テスト科目</t>
-  </si>
-  <si>
-    <t>保存：値が保存され、画面の表示：保存後の内容に更新</t>
-  </si>
-  <si>
-    <t>画面設計 3.9、処理フロー 2.20</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、テスト名：一時</t>
-  </si>
-  <si>
-    <t>表：保存されている値で表示し直される、変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計 3.9、処理フロー 2.21</t>
+    <t>画面設計：3.9
+処理フロー：2.25</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+テストの表のテスト名：テスト科目</t>
+  </si>
+  <si>
+    <t>保存：値が保存され
+画面の表示：保存後の内容に更新</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.20</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+テストの表のテスト名：一時</t>
+  </si>
+  <si>
+    <t>表：保存されている値で表示し直される
+変えた内容：消える</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.21</t>
   </si>
   <si>
     <t>同期実行（ユーザー）を押します。</t>
   </si>
   <si>
-    <t>画面設計 3.9、処理フロー 2.22</t>
+    <t>画面設計：3.9
+処理フロー：2.22</t>
   </si>
 </sst>
 </file>
@@ -927,13 +1000,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{333E9246-38A9-4CD1-AB59-9C47B4B25178}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443DF84-D8B4-47B7-923B-A32B55C9B347}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" customWidth="1"/>
+    <col min="2" max="3" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -1047,23 +1119,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{333E9246-38A9-4CD1-AB59-9C47B4B25178}"/>
+  <autoFilter ref="A1:C10" xr:uid="{4443DF84-D8B4-47B7-923B-A32B55C9B347}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161E8B2F-E387-400B-8153-E2F07EFF48A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1782E585-9F81-48F3-B137-DCF5329F45BA}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1101,13 +1171,13 @@
         <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
@@ -1124,13 +1194,13 @@
         <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
@@ -1147,13 +1217,13 @@
         <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
@@ -1170,13 +1240,13 @@
         <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
@@ -1190,16 +1260,16 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>95</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
@@ -1213,16 +1283,16 @@
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
@@ -1239,13 +1309,13 @@
         <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>33</v>
@@ -1262,36 +1332,34 @@
         <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{161E8B2F-E387-400B-8153-E2F07EFF48A0}"/>
+  <autoFilter ref="A1:G9" xr:uid="{1782E585-9F81-48F3-B137-DCF5329F45BA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7371E5B0-708E-43F2-82B4-64ED137C7ED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269F9388-F6F6-4F69-81FD-11CD5C60BB71}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1318,7 +1386,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1364,7 +1432,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1456,7 +1524,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1480,23 +1548,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{7371E5B0-708E-43F2-82B4-64ED137C7ED9}"/>
+  <autoFilter ref="A1:G8" xr:uid="{269F9388-F6F6-4F69-81FD-11CD5C60BB71}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73973E9-048C-4A3F-B70C-397743D575B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81DFF8F3-5ECB-44A9-90A7-D76B73A055F5}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1523,7 +1589,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1708,23 +1774,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{C73973E9-048C-4A3F-B70C-397743D575B9}"/>
+  <autoFilter ref="A1:G9" xr:uid="{81DFF8F3-5ECB-44A9-90A7-D76B73A055F5}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82F7360-E935-43B5-B80B-1DE5B32F67A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA62BCA-A003-4DE0-B54A-C923AC03E72B}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1798,23 +1862,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{A82F7360-E935-43B5-B80B-1DE5B32F67A5}"/>
+  <autoFilter ref="A1:G3" xr:uid="{BCA62BCA-A003-4DE0-B54A-C923AC03E72B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CADEC8D6-DCEC-42EB-8CBA-F1324D4E5A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20AA060E-808D-406E-AC5F-47371AE92F14}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1841,7 +1903,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1980,23 +2042,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{CADEC8D6-DCEC-42EB-8CBA-F1324D4E5A76}"/>
+  <autoFilter ref="A1:G7" xr:uid="{20AA060E-808D-406E-AC5F-47371AE92F14}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C41AE79-1132-4A99-BA51-11C84C83D610}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D478F7CA-1CA7-4F1B-BC01-4C685E926C4B}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2070,23 +2130,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{3C41AE79-1132-4A99-BA51-11C84C83D610}"/>
+  <autoFilter ref="A1:G3" xr:uid="{D478F7CA-1CA7-4F1B-BC01-4C685E926C4B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B2D6D4-A6F8-4D2D-95A7-ED991BE2A450}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C8A40E-0B64-42F1-A72B-094389FE6FF0}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2182,7 +2240,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2205,7 +2263,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -2229,23 +2287,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{36B2D6D4-A6F8-4D2D-95A7-ED991BE2A450}"/>
+  <autoFilter ref="A1:G6" xr:uid="{24C8A40E-0B64-42F1-A72B-094389FE6FF0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9EC0D8-52E7-45E7-9F08-0CE50DFDE6C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7702F3F-8D73-468F-B4FD-406607DA5EE2}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2319,23 +2375,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{0A9EC0D8-52E7-45E7-9F08-0CE50DFDE6C5}"/>
+  <autoFilter ref="A1:G3" xr:uid="{B7702F3F-8D73-468F-B4FD-406607DA5EE2}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F26DD6-5988-4F15-8821-C472EFAEB4F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C02FD09-3401-4558-A297-B8D0F502F955}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="60.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2431,7 +2485,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2477,7 +2531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -2523,7 +2577,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2577,13 +2631,13 @@
         <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>109</v>
@@ -2594,19 +2648,19 @@
     </row>
     <row r="12" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>118</v>
@@ -2615,21 +2669,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>118</v>
@@ -2640,19 +2694,19 @@
     </row>
     <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>121</v>
@@ -2661,7 +2715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -2669,13 +2723,13 @@
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>123</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>125</v>
@@ -2685,7 +2739,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15" xr:uid="{12F26DD6-5988-4F15-8821-C472EFAEB4F4}"/>
+  <autoFilter ref="A1:G15" xr:uid="{3C02FD09-3401-4558-A297-B8D0F502F955}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2565F68D-E3AA-4131-BB95-0802A571851E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFF6B65E-9DC7-4F27-AFBF-0B6AE9213297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA2D2DF-F680-4A22-A86A-98340D92839F}"/>
+    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{6C994496-6754-46FA-AEA6-0B69E5F1ECD6}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,13 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（実施結果取得）'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（実施状況確認）'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（実施状況確認）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（実施結果集計）'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（経年比較）'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（経年比較）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="396">
   <si>
     <t>通番</t>
   </si>
@@ -102,10 +102,13 @@
     <t>環境設定（共通）</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>環境設定（グループ別）</t>
   </si>
   <si>
-    <t>14</t>
+    <t>28</t>
   </si>
   <si>
     <t>9</t>
@@ -142,13 +145,22 @@
 実施結果集計-テスト：あり
 実施結果集計-アンケート：あり
 実施結果集計-投稿：なし
-経年比較-アンケート・テスト：なし</t>
-  </si>
-  <si>
-    <t>実行を押します。</t>
-  </si>
-  <si>
-    <t>処理ごとの状態：成功または警告</t>
+経年比較-アンケート・テスト：なし
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（実施結果取得-テスト）：成功または警告
+状態（実施結果取得-アンケート）：成功または警告
+状態（実施状況確認-テスト・アンケート）：成功または警告
+状態（実施結果集計-テスト）：成功または警告
+状態（実施結果集計-アンケート）：成功または警告
+取得結果（テスト）：nttdata-univ-material_results*.csv
+取得結果（アンケート）：nttdata-univ-class_results*.csv
+ファイル（テスト）：ok-テスト結果.xlsx
+ファイル（アンケート）：ok-アンケート結果.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -159,40 +171,75 @@
   </si>
   <si>
     <t>対象のグループ：ok
-実施結果取得-テスト：なし</t>
-  </si>
-  <si>
-    <t>実施結果取得-テストの状態：（空）
+実施結果取得-テスト：なし
+実施結果取得-アンケート：あり
+実施状況確認-テスト・アンケート：あり
+実施結果集計-テスト：あり
+実施結果集計-アンケート：あり
+実施結果集計-投稿：なし
+経年比較-アンケート・テスト：なし
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実施結果取得-テスト」のチェックを外して、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（実施結果取得-テスト）：スキップ
 ほかの処理：実行される</t>
   </si>
   <si>
     <t>対象のグループ：ok
-実施結果集計-投稿：あり</t>
-  </si>
-  <si>
-    <t>実施結果集計-投稿の状態：成功または警告</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok</t>
-  </si>
-  <si>
-    <t>実行が終わったあと、処理ごとの状態を確認します。</t>
-  </si>
-  <si>
-    <t>処理ごとの状態：成功、警告、失敗のいずれか</t>
-  </si>
-  <si>
-    <t>実行が終わったあと、ログ欄を確認します。</t>
-  </si>
-  <si>
-    <t>画面下部のログ：実行の結果
-ログの出力先：実行ログ</t>
-  </si>
-  <si>
-    <t>すべての行の「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：処理の結果のフォルダ、または投稿先のスレッド</t>
+実施結果取得-テスト：あり
+実施結果取得-アンケート：あり
+実施状況確認-テスト・アンケート：あり
+実施結果集計-テスト：あり
+実施結果集計-アンケート：あり
+実施結果集計-投稿：あり
+経年比較-アンケート・テスト：なし
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実施結果集計-投稿」にチェックを入れて、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（実施結果集計-投稿）：成功または警告</t>
+  </si>
+  <si>
+    <t>状態（実施結果取得-テスト）：成功、警告、失敗のいずれか
+状態（実施結果取得-アンケート）：成功、警告、失敗のいずれか
+状態（実施状況確認-テスト・アンケート）：成功、警告、失敗のいずれか
+状態（実施結果集計-テスト）：成功、警告、失敗のいずれか
+状態（実施結果集計-アンケート）：成功、警告、失敗のいずれか</t>
+  </si>
+  <si>
+    <t>状態（実施結果取得-テスト）：成功または警告
+状態（実施結果取得-アンケート）：成功または警告
+状態（実施状況確認-テスト・アンケート）：成功または警告
+状態（実施結果集計-テスト）：成功または警告
+状態（実施結果集計-アンケート）：成功または警告</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+実施結果取得-テスト：あり
+実施結果取得-アンケート：あり
+実施状況確認-テスト・アンケート：あり
+実施結果集計-テスト：あり
+実施結果集計-アンケート：あり
+実施結果集計-投稿：あり
+経年比較-アンケート・テスト：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押した後で、すべての行の「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：開く（実施結果取得-テスト）：結果のフォルダ
+開く（実施結果取得-アンケート）：結果のフォルダ
+開く（実施状況確認-テスト・アンケート）：結果のフォルダ
+開く（実施結果集計-テスト）：結果のフォルダ
+開く（実施結果集計-アンケート）：結果のフォルダ
+開く（実施結果集計-投稿）：投稿先のスレッド
+開く（経年比較-アンケート・テスト）：結果のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.1</t>
@@ -201,22 +248,37 @@
     <t>異常系</t>
   </si>
   <si>
-    <t>対象のグループ：ng</t>
-  </si>
-  <si>
-    <t>実施結果取得-テストの状態：失敗
-後続の処理：実行される</t>
-  </si>
-  <si>
-    <t>状態：成功または警告
-取得結果：テストの実施結果</t>
+    <t>対象のグループ：ng
+実施結果取得-テスト：あり
+実施結果取得-アンケート：あり
+実施状況確認-テスト・アンケート：あり
+実施結果集計-テスト：あり
+実施結果集計-アンケート：あり
+実施結果集計-投稿：なし
+経年比較-アンケート・テスト：なし
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>状態（実施結果取得-テスト）：失敗
+状態（実施結果取得-アンケート）：成功、警告、失敗のいずれか</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行（テスト）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（テスト）：成功または警告
+取得結果（テスト）：nttdata-univ-material_results*.csv が作られる</t>
   </si>
   <si>
     <t>画面設計：3.2
 処理フロー：2.2</t>
   </si>
   <si>
-    <t>実行が終わったあと、開くを押します。</t>
+    <t>「対象のグループ」を設定した後で、「実行（テスト）」を押した後で、「開く（テスト）」を押します。</t>
   </si>
   <si>
     <t>開いた画面：取得した結果のフォルダ</t>
@@ -225,47 +287,81 @@
     <t>画面設計：3.2</t>
   </si>
   <si>
-    <t>状態：成功または警告
-取得結果：アンケートの実施結果</t>
+    <t>「対象のグループ」を設定した後で、「実行（アンケート）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（アンケート）：成功または警告
+取得結果（アンケート）：nttdata-univ-class_results*.csv が作られる</t>
   </si>
   <si>
     <t>画面設計：3.2
 処理フロー：2.3</t>
   </si>
   <si>
-    <t>状態：成功または警告</t>
+    <t>「対象のグループ」を設定した後で、「実行（アンケート）」を押した後で、「開く（アンケート）」を押します。</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行（取得状況確認）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（取得状況確認）：成功または警告</t>
   </si>
   <si>
     <t>画面設計：3.2
 処理フロー：2.4</t>
   </si>
   <si>
-    <t>テストの実行を押します。</t>
-  </si>
-  <si>
-    <t>状態：失敗
-取得結果：なし</t>
-  </si>
-  <si>
-    <t>アンケートの実行を押します。</t>
+    <t>対象のグループ：ok
+取得結果（テスト）：ok-result.csv
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行（取得状況確認）」を押した後で、「開く（取得状況確認）」を押します。</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>状態（テスト）：失敗</t>
+  </si>
+  <si>
+    <t>状態（アンケート）：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+取得結果（テスト）：ok-result.csv
+取得結果（アンケート）：ok-result.csv
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>状態：成功または警告
-統合結果：取得した結果</t>
+ファイル：ok-統合結果.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.3
 処理フロー：2.5</t>
   </si>
   <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
+  </si>
+  <si>
     <t>開いた画面：統合結果のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.3</t>
   </si>
   <si>
-    <t>状態：成功または警告
-集計結果：テストの集計結果</t>
+    <t>対象のグループ：ok
+取得結果：なし
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：成功</t>
+  </si>
+  <si>
+    <t>状態（テスト）：成功または警告
+ファイル：ok-テスト結果.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -278,8 +374,8 @@
     <t>画面設計：3.4</t>
   </si>
   <si>
-    <t>状態：成功または警告
-集計結果：アンケートの集計結果</t>
+    <t>状態（アンケート）：成功または警告
+ファイル：ok-アンケート結果.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -289,115 +385,757 @@
     <t>開いた画面：アンケート集計結果のフォルダ</t>
   </si>
   <si>
-    <t>状態：成功または警告
-投稿：集計結果が投稿先のスレッドに投稿される</t>
+    <t>対象のグループ：ok
+集計結果（テスト）：ok-テスト結果.xlsx
+集計結果（アンケート）：ok-アンケート結果.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（投稿）：成功または警告</t>
   </si>
   <si>
     <t>画面設計：3.4
 処理フロー：2.8</t>
   </si>
   <si>
+    <t>「対象のグループ」を設定した後で、「実行（投稿）」を押した後で、「開く（投稿）」を押します。</t>
+  </si>
+  <si>
     <t>開いた画面：投稿先のスレッド（ブラウザ）</t>
   </si>
   <si>
     <t>対象のグループ：ok
-対象の会社名：空</t>
+対象の会社名：空
+比較年：1
+表示順：昇順
+元データ：ok-2025.xlsx、ok-2026.xlsx
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>状態：成功または警告
-経年比較の結果：作られる</t>
+ファイル：ok-2026-経年比較結果.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.5
 処理フロー：2.9</t>
   </si>
   <si>
+    <t>対象のグループ：ok
+比較年：1
+表示順：昇順
+元データ：ok-2025.xlsx、ok-2026.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
     <t>開いた画面：経年比較の結果のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.5</t>
   </si>
   <si>
-    <t>ログのファイルがない状態で、すべて削除を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「削除対象のログファイルがありません。」
-処理：終わる</t>
+    <t>対象のグループ：ok
+比較年：1
+表示順：昇順
+元データ：ok-2025.xlsx（なし）、ok-2026.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：成功
+ファイル：ok-2026-経年比較結果.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>確認：いいえ</t>
+  </si>
+  <si>
+    <t>ログのファイルがある状態で、「すべて削除」を押し、確認で「いいえ」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：残る</t>
   </si>
   <si>
     <t>画面設計：3.6
 処理フロー：2.10</t>
   </si>
   <si>
-    <t>確認：いいえ</t>
-  </si>
-  <si>
-    <t>ログのファイルがある状態で、すべて削除を押します。</t>
-  </si>
-  <si>
-    <t>削除：なし
-ログのファイル：残る</t>
-  </si>
-  <si>
     <t>確認：はい</t>
   </si>
   <si>
-    <t>ログのファイル：すべて削除される</t>
-  </si>
-  <si>
-    <t>対象のグループ：すべて、ok、ng</t>
-  </si>
-  <si>
-    <t>対象のグループを選びます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
+    <t>ログのファイルがある状態で、「すべて削除」を押し、確認で「はい」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：すべて削除される</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok
+処理：実施結果取得-テスト</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を切り替えます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ</t>
   </si>
   <si>
     <t>画面設計：3.6</t>
   </si>
   <si>
-    <t>処理のラジオボタンを切り替えます。</t>
+    <t>対象のグループ：すべて
+処理：実施結果取得-テスト、実施結果取得-アンケート、実施結果取得-取得状況確認、実施状況確認-テスト・アンケート、実施結果集計-テスト、実施結果集計-アンケート、実施結果集計-投稿、経年比較-アンケート・テスト、マスター同期</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「処理」のラジオボタンを「実施結果取得-テスト」、「実施結果取得-アンケート」、「実施結果取得-取得状況確認」、「実施状況確認-テスト・アンケート」、「実施結果集計-テスト」、「実施結果集計-アンケート」、「実施結果集計-投稿」、「経年比較-アンケート・テスト」、「マスター同期」、「実施結果取得-テスト」の順に切り替えます。</t>
   </si>
   <si>
     <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
   </si>
   <si>
-    <t>テスト結果ファイル名の接尾語：saved</t>
-  </si>
-  <si>
-    <t>保存を押します。</t>
-  </si>
-  <si>
-    <t>保存先：bats\common.bat
-画面の表示：保存後の内容に更新</t>
+    <t>対象のグループ：すべて
+処理：実施結果取得-テスト</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、ログのファイルがない状態で、「すべて削除」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「削除対象のログファイルがありません。」</t>
+  </si>
+  <si>
+    <t>グループデータのフォルダ：saved-client-data
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に ClientDataRootDir=saved-client-data が保存される
+状態（保存）：完了</t>
   </si>
   <si>
     <t>画面設計：3.7
 処理フロー：2.11</t>
   </si>
   <si>
-    <t>テスト結果ファイル名の接尾語：tmp</t>
-  </si>
-  <si>
-    <t>再読込を押します。</t>
-  </si>
-  <si>
-    <t>入力欄：保存されている値
-変えた内容：消える</t>
+    <t>グループデータのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「グループデータのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>グループデータのフォルダ：%BASE_PATH%clients（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>画面設計：3.7
 処理フロー：2.12</t>
   </si>
   <si>
-    <t>新しい名前：TrackNew</t>
-  </si>
-  <si>
-    <t>新規作成を押します。</t>
-  </si>
-  <si>
-    <t>一覧：新しい名前が追加され、選ばれる</t>
+    <t>テンプレートのフォルダ：saved-template
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テンプレートのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に TemplateRootDir=saved-template が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>テンプレートのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テンプレートのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テンプレートのフォルダ：%BASE_PATH%template（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>ログの出力先：saved-log
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「ログの出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に CommonLogPath=saved-log が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>ログの出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「ログの出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログの出力先：%BASE_PATH%logs（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>実施結果の取得先（共通）：saved-result-root
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「実施結果の取得先（共通）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に ResultRootDir=saved-result-root が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>実施結果の取得先（共通）：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「実施結果の取得先（共通）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>実施結果の取得先（共通）：%BASE_PATH%output\実施結果（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>テスト結果の取得先：saved-test-result-root
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テスト結果の取得先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に TestResultRootDir=saved-test-result-root が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>テスト結果の取得先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テスト結果の取得先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テスト結果の取得先：%ResultRootDir%\01_テスト（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>アンケート結果の取得先：saved-survey-result-root
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アンケート結果の取得先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に SurveyResultRootDir=saved-survey-result-root が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>アンケート結果の取得先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アンケート結果の取得先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>アンケート結果の取得先：%ResultRootDir%\02_アンケート（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>集計結果の出力先（共通）：saved-output-root
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「集計結果の出力先（共通）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputRootDir=saved-output-root が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>集計結果の出力先（共通）：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「集計結果の出力先（共通）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>集計結果の出力先（共通）：%BASE_PATH%output\集計結果（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>テスト集計結果の出力先：saved-output-test
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テスト集計結果の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputTestCollectDir=saved-output-test が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>テスト集計結果の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テスト集計結果の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テスト集計結果の出力先：%OutputRootDir%\テスト（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>テスト結果ファイル名の接尾語：saved-test-suffix
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テスト結果ファイル名の接尾語」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputTestResultFileSuffix=saved-test-suffix が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>テスト結果ファイル名の接尾語：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テスト結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テスト結果ファイル名の接尾語：テスト結果（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>アンケート集計結果の出力先：saved-output-survey
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アンケート集計結果の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputSurveyCollectDir=saved-output-survey が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>アンケート集計結果の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アンケート集計結果の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>アンケート集計結果の出力先：%OutputRootDir%\アンケート（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>アンケート結果ファイル名の接尾語：saved-survey-suffix
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アンケート結果ファイル名の接尾語」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputSurveyResultFileSuffix=saved-survey-suffix が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>アンケート結果ファイル名の接尾語：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アンケート結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>アンケート結果ファイル名の接尾語：アンケート結果（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>統合結果の出力先：saved-output-combine
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「統合結果の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputCombineCollectDir=saved-output-combine が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>統合結果の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「統合結果の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>統合結果の出力先：%OutputRootDir%\統合（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>統合結果ファイル名の接尾語：saved-combine-suffix
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「統合結果ファイル名の接尾語」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputCombineResultFileSuffix=saved-combine-suffix が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>統合結果ファイル名の接尾語：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「統合結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>統合結果ファイル名の接尾語：統合結果（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>経年比較結果の出力先：saved-year-output
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較結果の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputYearComparisonCollectDir=saved-year-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>経年比較結果の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較結果の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>経年比較結果の出力先：%OutputRootDir%\経年比較（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>経年比較結果ファイル名の接尾語：saved-year-suffix
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較結果ファイル名の接尾語」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に OutputYearComparisonResultFileSuffix=saved-year-suffix が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>経年比較結果ファイル名の接尾語：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>経年比較結果ファイル名の接尾語：経年比較結果（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>経年比較の比較年数：saved-compare-period
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較の比較年数」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に ComparePeriod=saved-compare-period が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>経年比較の比較年数：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較の比較年数」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>経年比較の比較年数：1（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>経年比較の年度表示順：昇順
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較の年度表示順」で「昇順」を選んだ後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に YearOrder=0 が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>経年比較のコースグループ：saved-course-group
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較のコースグループ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に CourseGroupDefs=saved-course-group が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>経年比較のコースグループ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「経年比較のコースグループ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>経年比較のコースグループ：ビジネス:ビジネス基礎,…（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>trackログインURL：saved-login-url
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「trackログインURL」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に TrackLoginUrl=saved-login-url が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>trackログインURL：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「trackログインURL」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>trackログインURL：https://nttdata-univ.train.tracks.run/auth/login（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>trackダウンロード用スクリプトのパス：saved-script-path
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「trackダウンロード用スクリプトのパス」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に AutoHotkeyScriptPath=saved-script-path が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>trackダウンロード用スクリプトのパス：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「trackダウンロード用スクリプトのパス」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>trackダウンロード用スクリプトのパス：%BASE_PATH%AutoHotkey\scripts\download.ahk（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>trackダウンロード用実行ファイルのパス：saved-exe-path
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「trackダウンロード用実行ファイルのパス」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に AutoHotkeyExePath=saved-exe-path が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>trackダウンロード用実行ファイルのパス：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「trackダウンロード用実行ファイルのパス」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>trackダウンロード用実行ファイルのパス：%BASE_PATH%AutoHotkey\v2\AutoHotkey.exe（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>合格点：saved-pass-score
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「合格点」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に PassScore=saved-pass-score が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>合格点：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「合格点」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>合格点：80（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>入力なし</t>
+  </si>
+  <si>
+    <t>「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>「trackダウンロード用スクリプトのパス」の「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：download.ahk</t>
+  </si>
+  <si>
+    <t>画面設計：3.7</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat
+グループ名：TestNew</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：グループ名が追加され、選ばれる</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -405,26 +1143,66 @@
   </si>
   <si>
     <t>対象のグループ：ok
-新しい名前：TrackCopy</t>
-  </si>
-  <si>
-    <t>保存済みのグループを選び、コピーを押します。</t>
-  </si>
-  <si>
-    <t>一覧：新しいグループが 1 つだけ追加され、選ばれる
-設定ファイルと Excel ファイル：コピーされる</t>
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx
+グループ名：TestCopy</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：新しいグループが追加され、選ばれる
+設定ファイル：TestCopy.bat が作られる
+Excel ファイル：TestCopy.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.14</t>
   </si>
   <si>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「再読込」を押して、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.17</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok、入力なし（保存されている投稿先）
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト投稿」を押します。</t>
+  </si>
+  <si>
+    <t>状態（テスト投稿）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.19</t>
+  </si>
+  <si>
     <t>対象のグループ：ok
-サブドメイン：saved</t>
-  </si>
-  <si>
-    <t>設定ファイル：値が保存される
-画面の表示：保存後の内容に更新</t>
+サブドメイン：saved-subdomain
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に KintoneSubdomain=saved-subdomain が保存される
+画面の表示：保存後の内容に更新
+状態（保存）：完了</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -432,176 +1210,366 @@
   </si>
   <si>
     <t>対象のグループ：ok
-サブドメイン：tmp</t>
+サブドメイン：tmp-reload
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>サブドメイン：iiglepv0966f（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.16</t>
   </si>
   <si>
-    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
-  </si>
-  <si>
-    <t>テスト接続（認証情報）を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功</t>
-  </si>
-  <si>
-    <t>画面設計：3.8
-処理フロー：2.17</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
-対象アプリID：136</t>
-  </si>
-  <si>
-    <t>テスト接続（ユーザー）を押します。</t>
+ログイン名：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ログイン名：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログイン名：user01（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パスワード：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintonePassword が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スペースID：saved-space-id
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に SpaceId=saved-space-id が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スペースID：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿先スペースID：3（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スレッドID：saved-thread-id
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スレッドID」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に ThreadId=saved-thread-id が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スレッドID：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スレッドID」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿先スレッドID：229（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿コメント文言：saved-comment
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿コメント文言」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に CommentTextTemplate=saved-comment が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿コメント文言：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿コメント文言」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿コメント文言：集計結果を更新しました。（{グループ名}）（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の年度表示順：昇順
+対象アプリID：136
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID」を設定した後で、「テスト接続（ユーザー）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（ユーザー）：成功</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.18</t>
   </si>
   <si>
-    <t>対象のグループ：ok、入力なし（保存されている投稿先）</t>
-  </si>
-  <si>
-    <t>テスト投稿を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功
-投稿：テスト用のコメント</t>
-  </si>
-  <si>
-    <t>画面設計：3.8
-処理フロー：2.19</t>
-  </si>
-  <si>
-    <t>ok（既存のグループ名）</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」
-一覧：追加されない</t>
-  </si>
-  <si>
-    <t>新規作成を押したあと、キャンセルを押します。</t>
+    <t>対象のグループ：ok
+対象アプリID（ユーザー）：saved-app-id
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に SyncUserMasterAppId=saved-app-id が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（ユーザー）：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>対象アプリID（ユーザー）：136（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の比較年数：saved-compare-period
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「経年比較の比較年数」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に ComparePeriod=saved-compare-period が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の比較年数：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「経年比較の比較年数」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>経年比較の比較年数：空（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
   </si>
   <si>
     <t>一覧：変わらない</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>新しい名前：TrackUnsaved</t>
-  </si>
-  <si>
-    <t>新規作成直後の、まだ保存していないグループを選び、コピーを押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「コピー元のグループが存在しません。」
-コピー：行われない</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
-サブドメイン：空</t>
-  </si>
-  <si>
-    <t>状態：失敗
-接続：行われない</t>
-  </si>
-  <si>
-    <t>12</t>
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat
+グループ名：TestUnsaved</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「コピー」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません。」</t>
   </si>
   <si>
     <t>対象のグループ：ok
-パスワード：wrong-password</t>
-  </si>
-  <si>
-    <t>状態：失敗</t>
-  </si>
-  <si>
-    <t>13</t>
+サブドメイン：空
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: サブドメイン・ログイン名・パスワードをすべて入力してください。」
+状態（認証情報）：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ok
-対象アプリID：空</t>
+パスワード：誤った値
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ok
-投稿先スペースID：空</t>
-  </si>
-  <si>
-    <t>状態：失敗
-投稿：行われない</t>
-  </si>
-  <si>
-    <t>テストの表で、追加（テスト）を押します。</t>
-  </si>
-  <si>
-    <t>表：末尾に空の行が追加される</t>
+投稿先スペースID：空
+経年比較の年度表示順：昇順
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: スペースID／スレッドIDを入力してください。」
+状態（テスト投稿）：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+経年比較の年度表示順：昇順
+対象アプリID：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト接続（ユーザー）」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: 対象アプリIDを入力してください。」
+状態（ユーザー）：失敗</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「同期実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（同期実行）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.22</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、テストの表で「追加（テスト）」を押します。</t>
+  </si>
+  <si>
+    <t>表：末尾に空の行が追加される（未確認）</t>
   </si>
   <si>
     <t>画面設計：3.9
 処理フロー：2.24</t>
   </si>
   <si>
-    <t>テストの表で、行を選んで削除（テスト）を押します。</t>
-  </si>
-  <si>
-    <t>表：選んだ行が削除される</t>
+    <t>「対象のグループ」を設定した後で、テストの表の1行目の「削除（テスト）」を押します。</t>
+  </si>
+  <si>
+    <t>表：その行が削除される</t>
   </si>
   <si>
     <t>画面設計：3.9
 処理フロー：2.23</t>
   </si>
   <si>
-    <t>アンケートの表で、追加（アンケート）を押します。</t>
+    <t>対象のグループ：ok
+テスト名（1行目）：saved-subject
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「テスト名（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>テスト名（1行目）：saved-subject が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.20</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+テスト名：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「テスト名（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テスト名（1行目）：社会を支えるITサービス（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.21</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、アンケートの表で「追加（アンケート）」を押します。</t>
   </si>
   <si>
     <t>画面設計：3.9
 処理フロー：2.26</t>
   </si>
   <si>
-    <t>アンケートの表で、行を選んで削除（アンケート）を押します。</t>
+    <t>「対象のグループ」を設定した後で、アンケートの表の2行目の「削除（アンケート）」を押します。</t>
+  </si>
+  <si>
+    <t>表：2行目（48693-639607）が削除される</t>
   </si>
   <si>
     <t>画面設計：3.9
 処理フロー：2.25</t>
   </si>
   <si>
-    <t>対象のグループ：ok
-テストの表のテスト名：テスト科目</t>
-  </si>
-  <si>
-    <t>保存：値が保存され
-画面の表示：保存後の内容に更新</t>
-  </si>
-  <si>
-    <t>画面設計：3.9
-処理フロー：2.20</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-テストの表のテスト名：一時</t>
-  </si>
-  <si>
-    <t>表：保存されている値で表示し直される
-変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計：3.9
-処理フロー：2.21</t>
-  </si>
-  <si>
-    <t>同期実行（ユーザー）を押します。</t>
-  </si>
-  <si>
-    <t>画面設計：3.9
-処理フロー：2.22</t>
+    <t>状態（同期実行）：失敗</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: 対象アプリIDが設定されていません。」
+状態（同期実行）：失敗</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443DF84-D8B4-47B7-923B-A32B55C9B347}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19916CC6-FD53-4DD3-8A68-BBE1F293D263}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1049,7 +2017,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="54" x14ac:dyDescent="0.45">
@@ -1071,7 +2039,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -1093,7 +2061,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="54" x14ac:dyDescent="0.45">
@@ -1101,40 +2069,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{4443DF84-D8B4-47B7-923B-A32B55C9B347}"/>
+  <autoFilter ref="A1:C10" xr:uid="{19916CC6-FD53-4DD3-8A68-BBE1F293D263}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1782E585-9F81-48F3-B137-DCF5329F45BA}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104756DA-E496-46FF-BA85-B356138FBBFC}">
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1142,225 +2110,248 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>144</v>
+        <v>372</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>145</v>
+        <v>373</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>146</v>
+        <v>374</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>147</v>
+        <v>375</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>148</v>
+        <v>376</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>149</v>
+        <v>377</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>378</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>145</v>
+        <v>379</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>151</v>
+        <v>380</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>381</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>152</v>
+        <v>382</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>148</v>
+        <v>383</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>153</v>
+        <v>384</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>154</v>
+        <v>385</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>95</v>
+        <v>386</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>155</v>
+        <v>387</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>156</v>
+        <v>388</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>389</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>158</v>
+        <v>376</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>159</v>
+        <v>390</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>160</v>
+        <v>391</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>392</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>161</v>
+        <v>393</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>33</v>
+      <c r="C10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{1782E585-9F81-48F3-B137-DCF5329F45BA}"/>
+  <autoFilter ref="A1:G10" xr:uid="{104756DA-E496-46FF-BA85-B356138FBBFC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269F9388-F6F6-4F69-81FD-11CD5C60BB71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1B4592-3167-4CDE-85FE-7826B6CFB9FF}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1368,22 +2359,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -1391,179 +2382,179 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{269F9388-F6F6-4F69-81FD-11CD5C60BB71}"/>
+  <autoFilter ref="A1:G8" xr:uid="{7B1B4592-3167-4CDE-85FE-7826B6CFB9FF}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81DFF8F3-5ECB-44A9-90A7-D76B73A055F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DA9A8AA-5DD3-4715-92DC-AD08CE9C940C}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1571,225 +2562,225 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{81DFF8F3-5ECB-44A9-90A7-D76B73A055F5}"/>
+  <autoFilter ref="A1:G9" xr:uid="{1DA9A8AA-5DD3-4715-92DC-AD08CE9C940C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA62BCA-A003-4DE0-B54A-C923AC03E72B}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5756211-5D07-416D-95DE-146B56DAFCBA}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1797,87 +2788,110 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{BCA62BCA-A003-4DE0-B54A-C923AC03E72B}"/>
+  <autoFilter ref="A1:G4" xr:uid="{E5756211-5D07-416D-95DE-146B56DAFCBA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20AA060E-808D-406E-AC5F-47371AE92F14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A5D622-38B5-47B9-BE35-26B5014ADE6A}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1885,179 +2899,179 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{20AA060E-808D-406E-AC5F-47371AE92F14}"/>
+  <autoFilter ref="A1:G7" xr:uid="{92A5D622-38B5-47B9-BE35-26B5014ADE6A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D478F7CA-1CA7-4F1B-BC01-4C685E926C4B}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC911610-5370-48D2-AC84-2920596BBA65}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2065,87 +3079,110 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{D478F7CA-1CA7-4F1B-BC01-4C685E926C4B}"/>
+  <autoFilter ref="A1:G4" xr:uid="{DC911610-5370-48D2-AC84-2920596BBA65}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C8A40E-0B64-42F1-A72B-094389FE6FF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C78EB83-3479-450F-AFBC-F99E51DB8730}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2153,156 +3190,156 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{24C8A40E-0B64-42F1-A72B-094389FE6FF0}"/>
+  <autoFilter ref="A1:G6" xr:uid="{0C78EB83-3479-450F-AFBC-F99E51DB8730}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7702F3F-8D73-468F-B4FD-406607DA5EE2}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7112514B-8C8F-44E9-9D36-0C72F57C656B}">
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2310,87 +3347,1076 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A44" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{B7702F3F-8D73-468F-B4FD-406607DA5EE2}"/>
+  <autoFilter ref="A1:G46" xr:uid="{7112514B-8C8F-44E9-9D36-0C72F57C656B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C02FD09-3401-4558-A297-B8D0F502F955}">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6CD60B-24EF-4DB9-BB5A-0C0FE4B3B915}">
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2398,348 +4424,670 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>103</v>
+        <v>287</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>105</v>
+        <v>289</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>107</v>
+        <v>291</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>109</v>
+        <v>293</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>110</v>
+        <v>294</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>111</v>
+        <v>296</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>112</v>
+        <v>297</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>298</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>114</v>
+        <v>301</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>302</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>303</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>117</v>
+        <v>304</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>118</v>
+        <v>305</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
+        <v>306</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>117</v>
+        <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>121</v>
+        <v>309</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>123</v>
+        <v>311</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>124</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>125</v>
+        <v>305</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
+        <v>314</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>127</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>297</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="90" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="126" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="108" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>33</v>
+      <c r="B29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15" xr:uid="{3C02FD09-3401-4558-A297-B8D0F502F955}"/>
+  <autoFilter ref="A1:G29" xr:uid="{BE6CD60B-24EF-4DB9-BB5A-0C0FE4B3B915}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFF6B65E-9DC7-4F27-AFBF-0B6AE9213297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85214D4E-0F42-4EFC-9550-1B087F5508EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{6C994496-6754-46FA-AEA6-0B69E5F1ECD6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FE2258D7-CECA-4541-BD4E-C522E062856E}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="2.9 環境設定（マスター）" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（実施結果取得）'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（実施状況確認）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（実施結果集計）'!$A$1:$G$7</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="394">
   <si>
     <t>通番</t>
   </si>
@@ -160,7 +160,8 @@
 取得結果（テスト）：nttdata-univ-material_results*.csv
 取得結果（アンケート）：nttdata-univ-class_results*.csv
 ファイル（テスト）：ok-テスト結果.xlsx
-ファイル（アンケート）：ok-アンケート結果.xlsx が作られる</t>
+ファイル（アンケート）：ok-アンケート結果.xlsx が作られる
+状態：成功または警告</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -185,7 +186,11 @@
   </si>
   <si>
     <t>状態（実施結果取得-テスト）：スキップ
-ほかの処理：実行される</t>
+状態（実施結果取得-アンケート）：成功または警告
+状態（実施状況確認-テスト・アンケート）：成功または警告
+状態（実施結果集計-テスト）：成功または警告
+状態（実施結果集計-アンケート）：成功または警告
+状態：成功または警告</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -202,21 +207,13 @@
     <t>「対象のグループ」を設定した後で、「実施結果集計-投稿」にチェックを入れて、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態（実施結果集計-投稿）：成功または警告</t>
-  </si>
-  <si>
-    <t>状態（実施結果取得-テスト）：成功、警告、失敗のいずれか
-状態（実施結果取得-アンケート）：成功、警告、失敗のいずれか
-状態（実施状況確認-テスト・アンケート）：成功、警告、失敗のいずれか
-状態（実施結果集計-テスト）：成功、警告、失敗のいずれか
-状態（実施結果集計-アンケート）：成功、警告、失敗のいずれか</t>
-  </si>
-  <si>
     <t>状態（実施結果取得-テスト）：成功または警告
 状態（実施結果取得-アンケート）：成功または警告
 状態（実施状況確認-テスト・アンケート）：成功または警告
 状態（実施結果集計-テスト）：成功または警告
-状態（実施結果集計-アンケート）：成功または警告</t>
+状態（実施結果集計-アンケート）：成功または警告
+状態（実施結果集計-投稿）：成功または警告
+状態：成功または警告</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -233,13 +230,14 @@
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、すべての行の「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：開く（実施結果取得-テスト）：結果のフォルダ
+    <t>開く（実施結果取得-テスト）：結果のフォルダ
 開く（実施結果取得-アンケート）：結果のフォルダ
 開く（実施状況確認-テスト・アンケート）：結果のフォルダ
 開く（実施結果集計-テスト）：結果のフォルダ
 開く（実施結果集計-アンケート）：結果のフォルダ
 開く（実施結果集計-投稿）：投稿先のスレッド
-開く（経年比較-アンケート・テスト）：結果のフォルダ</t>
+開く（経年比較-アンケート・テスト）：結果のフォルダ
+状態：成功または警告</t>
   </si>
   <si>
     <t>画面設計：3.1</t>
@@ -260,7 +258,11 @@
   </si>
   <si>
     <t>状態（実施結果取得-テスト）：失敗
-状態（実施結果取得-アンケート）：成功、警告、失敗のいずれか</t>
+状態（実施結果取得-アンケート）：失敗
+状態（実施状況確認-テスト・アンケート）：成功
+状態（実施結果集計-テスト）：成功
+状態（実施結果集計-アンケート）：成功
+状態：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -526,7 +528,7 @@
     <t>「グループデータのフォルダ」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>グループデータのフォルダ：%BASE_PATH%clients（保存されている値）
+    <t>グループデータのフォルダ：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -553,7 +555,7 @@
     <t>「テンプレートのフォルダ」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>テンプレートのフォルダ：%BASE_PATH%template（保存されている値）
+    <t>テンプレートのフォルダ：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -576,7 +578,7 @@
     <t>「ログの出力先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>ログの出力先：%BASE_PATH%logs（保存されている値）
+    <t>ログの出力先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -599,7 +601,7 @@
     <t>「実施結果の取得先（共通）」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>実施結果の取得先（共通）：%BASE_PATH%output\実施結果（保存されている値）
+    <t>実施結果の取得先（共通）：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -625,7 +627,7 @@
     <t>「テスト結果の取得先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>テスト結果の取得先：%ResultRootDir%\01_テスト（保存されている値）
+    <t>テスト結果の取得先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -654,7 +656,7 @@
     <t>「アンケート結果の取得先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>アンケート結果の取得先：%ResultRootDir%\02_アンケート（保存されている値）
+    <t>アンケート結果の取得先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -683,7 +685,7 @@
     <t>「集計結果の出力先（共通）」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>集計結果の出力先（共通）：%BASE_PATH%output\集計結果（保存されている値）
+    <t>集計結果の出力先（共通）：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -712,7 +714,7 @@
     <t>「テスト集計結果の出力先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>テスト集計結果の出力先：%OutputRootDir%\テスト（保存されている値）
+    <t>テスト集計結果の出力先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -741,7 +743,7 @@
     <t>「テスト結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>テスト結果ファイル名の接尾語：テスト結果（保存されている値）
+    <t>テスト結果ファイル名の接尾語：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -770,7 +772,7 @@
     <t>「アンケート集計結果の出力先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>アンケート集計結果の出力先：%OutputRootDir%\アンケート（保存されている値）
+    <t>アンケート集計結果の出力先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -799,7 +801,7 @@
     <t>「アンケート結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>アンケート結果ファイル名の接尾語：アンケート結果（保存されている値）
+    <t>アンケート結果ファイル名の接尾語：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -828,7 +830,7 @@
     <t>「統合結果の出力先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>統合結果の出力先：%OutputRootDir%\統合（保存されている値）
+    <t>統合結果の出力先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -857,7 +859,7 @@
     <t>「統合結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>統合結果ファイル名の接尾語：統合結果（保存されている値）
+    <t>統合結果ファイル名の接尾語：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -883,7 +885,7 @@
     <t>「経年比較結果の出力先」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>経年比較結果の出力先：%OutputRootDir%\経年比較（保存されている値）
+    <t>経年比較結果の出力先：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -912,7 +914,7 @@
     <t>「経年比較結果ファイル名の接尾語」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>経年比較結果ファイル名の接尾語：経年比較結果（保存されている値）
+    <t>経年比較結果ファイル名の接尾語：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -941,7 +943,7 @@
     <t>「経年比較の比較年数」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>経年比較の比較年数：1（保存されている値）
+    <t>経年比較の比較年数：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -984,7 +986,7 @@
     <t>「経年比較のコースグループ」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>経年比較のコースグループ：ビジネス:ビジネス基礎,…（保存されている値）
+    <t>経年比較のコースグループ：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1013,7 +1015,7 @@
     <t>「trackログインURL」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>trackログインURL：https://nttdata-univ.train.tracks.run/auth/login（保存されている値）
+    <t>trackログインURL：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1042,7 +1044,7 @@
     <t>「trackダウンロード用スクリプトのパス」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>trackダウンロード用スクリプトのパス：%BASE_PATH%AutoHotkey\scripts\download.ahk（保存されている値）
+    <t>trackダウンロード用スクリプトのパス：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1071,7 +1073,7 @@
     <t>「trackダウンロード用実行ファイルのパス」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>trackダウンロード用実行ファイルのパス：%BASE_PATH%AutoHotkey\v2\AutoHotkey.exe（保存されている値）
+    <t>trackダウンロード用実行ファイルのパス：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1100,7 +1102,7 @@
     <t>「合格点」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>合格点：80（保存されている値）
+    <t>合格点：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1120,7 +1122,7 @@
     <t>「trackダウンロード用スクリプトのパス」の「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：download.ahk</t>
+    <t>開いた画面：（保存されている値のスクリプト名）</t>
   </si>
   <si>
     <t>画面設計：3.7</t>
@@ -1218,7 +1220,7 @@
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>サブドメイン：iiglepv0966f（保存されている値）
+    <t>サブドメイン：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1247,7 +1249,7 @@
     <t>「対象のグループ」と「ログイン名」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>ログイン名：user01（保存されている値）
+    <t>ログイン名：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1284,7 +1286,7 @@
     <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>投稿先スペースID：3（保存されている値）
+    <t>投稿先スペースID：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1309,7 +1311,7 @@
     <t>「対象のグループ」と「投稿先スレッドID」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>投稿先スレッドID：229（保存されている値）
+    <t>投稿先スレッドID：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1334,7 +1336,7 @@
     <t>「対象のグループ」と「投稿コメント文言」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>投稿コメント文言：集計結果を更新しました。（{グループ名}）（保存されている値）
+    <t>投稿コメント文言：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1375,7 +1377,7 @@
     <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>対象アプリID（ユーザー）：136（保存されている値）
+    <t>対象アプリID（ユーザー）：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1539,7 +1541,7 @@
     <t>「対象のグループ」と「テスト名（1行目）」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>テスト名（1行目）：社会を支えるITサービス（保存されている値）
+    <t>テスト名（1行目）：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
@@ -1968,7 +1970,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19916CC6-FD53-4DD3-8A68-BBE1F293D263}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F4C8DA-1875-4658-98AD-D64C541B8810}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2087,14 +2089,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{19916CC6-FD53-4DD3-8A68-BBE1F293D263}"/>
+  <autoFilter ref="A1:C10" xr:uid="{C9F4C8DA-1875-4658-98AD-D64C541B8810}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104756DA-E496-46FF-BA85-B356138FBBFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E235D6EC-62A0-4272-9E25-363DCBD67EC0}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2136,16 +2138,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2159,16 +2161,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2182,16 +2184,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2205,22 +2207,22 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -2228,16 +2230,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2251,16 +2253,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2274,16 +2276,16 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -2294,19 +2296,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -2317,34 +2319,34 @@
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10" xr:uid="{104756DA-E496-46FF-BA85-B356138FBBFC}"/>
+  <autoFilter ref="A1:G10" xr:uid="{E235D6EC-62A0-4272-9E25-363DCBD67EC0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1B4592-3167-4CDE-85FE-7826B6CFB9FF}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{778BB135-44B1-4EAE-906E-4843AE466A61}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -2454,16 +2456,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2474,16 +2476,16 @@
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>33</v>
@@ -2492,61 +2494,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{7B1B4592-3167-4CDE-85FE-7826B6CFB9FF}"/>
+  <autoFilter ref="A1:G6" xr:uid="{778BB135-44B1-4EAE-906E-4843AE466A61}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DA9A8AA-5DD3-4715-92DC-AD08CE9C940C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E283A024-47FC-4BF5-BA40-7D4F8D967351}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2588,16 +2544,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2611,16 +2567,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2634,16 +2590,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2657,16 +2613,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2680,16 +2636,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2703,16 +2659,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2723,19 +2679,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -2746,33 +2702,33 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{1DA9A8AA-5DD3-4715-92DC-AD08CE9C940C}"/>
+  <autoFilter ref="A1:G9" xr:uid="{E283A024-47FC-4BF5-BA40-7D4F8D967351}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5756211-5D07-416D-95DE-146B56DAFCBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45A692D-31CA-4754-A379-D6BB0A7EBB2C}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2814,16 +2770,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2837,16 +2793,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2860,30 +2816,30 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{E5756211-5D07-416D-95DE-146B56DAFCBA}"/>
+  <autoFilter ref="A1:G4" xr:uid="{A45A692D-31CA-4754-A379-D6BB0A7EBB2C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A5D622-38B5-47B9-BE35-26B5014ADE6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A3A448-3900-44D8-8BFB-F4E0FFC7B036}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2925,16 +2881,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2948,16 +2904,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2971,16 +2927,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2994,16 +2950,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3017,16 +2973,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -3040,30 +2996,30 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{92A5D622-38B5-47B9-BE35-26B5014ADE6A}"/>
+  <autoFilter ref="A1:G7" xr:uid="{47A3A448-3900-44D8-8BFB-F4E0FFC7B036}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC911610-5370-48D2-AC84-2920596BBA65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1892A1A-ABFC-477F-B731-E014E6D87E6E}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3105,16 +3061,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3128,16 +3084,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3151,30 +3107,30 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{DC911610-5370-48D2-AC84-2920596BBA65}"/>
+  <autoFilter ref="A1:G4" xr:uid="{D1892A1A-ABFC-477F-B731-E014E6D87E6E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C78EB83-3479-450F-AFBC-F99E51DB8730}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58010CD9-54DF-4D18-B46F-9C83DCEE22B9}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3216,16 +3172,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3239,16 +3195,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3262,16 +3218,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3285,16 +3241,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3305,33 +3261,33 @@
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{0C78EB83-3479-450F-AFBC-F99E51DB8730}"/>
+  <autoFilter ref="A1:G6" xr:uid="{58010CD9-54DF-4D18-B46F-9C83DCEE22B9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7112514B-8C8F-44E9-9D36-0C72F57C656B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF28050-F508-42CF-823C-A95D2136B99B}">
   <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3373,22 +3329,22 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3396,16 +3352,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3419,22 +3375,22 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -3442,16 +3398,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3465,22 +3421,22 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3488,16 +3444,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -3511,22 +3467,22 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3534,16 +3490,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -3557,39 +3513,39 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -3597,45 +3553,45 @@
     </row>
     <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -3643,45 +3599,45 @@
     </row>
     <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -3689,45 +3645,45 @@
     </row>
     <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -3735,45 +3691,45 @@
     </row>
     <row r="18" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -3781,45 +3737,45 @@
     </row>
     <row r="20" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -3827,45 +3783,45 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -3873,45 +3829,45 @@
     </row>
     <row r="24" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -3919,45 +3875,45 @@
     </row>
     <row r="26" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -3965,28 +3921,28 @@
     </row>
     <row r="28" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
@@ -3994,16 +3950,16 @@
         <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -4011,45 +3967,45 @@
     </row>
     <row r="30" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -4057,45 +4013,45 @@
     </row>
     <row r="32" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="F32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -4103,22 +4059,22 @@
     </row>
     <row r="34" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -4126,45 +4082,45 @@
     </row>
     <row r="35" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="B36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -4172,45 +4128,45 @@
     </row>
     <row r="37" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="F37" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="B38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="306" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -4218,45 +4174,45 @@
     </row>
     <row r="39" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="F39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="B40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="342" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>34</v>
@@ -4264,45 +4220,45 @@
     </row>
     <row r="41" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="F41" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="342" x14ac:dyDescent="0.45">
-      <c r="A42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>34</v>
@@ -4310,22 +4266,22 @@
     </row>
     <row r="43" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>34</v>
@@ -4333,22 +4289,22 @@
     </row>
     <row r="44" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>34</v>
@@ -4356,22 +4312,22 @@
     </row>
     <row r="45" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>34</v>
@@ -4385,30 +4341,30 @@
         <v>29</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>285</v>
-      </c>
       <c r="G46" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G46" xr:uid="{7112514B-8C8F-44E9-9D36-0C72F57C656B}"/>
+  <autoFilter ref="A1:G46" xr:uid="{7BF28050-F508-42CF-823C-A95D2136B99B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6CD60B-24EF-4DB9-BB5A-0C0FE4B3B915}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9AB410-9F98-4B57-8C01-BB56273A1DB6}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4450,16 +4406,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -4473,16 +4429,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -4496,16 +4452,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -4519,16 +4475,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -4542,16 +4498,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -4565,16 +4521,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -4588,22 +4544,22 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -4611,16 +4567,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -4634,16 +4590,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -4651,45 +4607,45 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -4697,45 +4653,45 @@
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -4743,45 +4699,45 @@
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -4789,22 +4745,22 @@
     </row>
     <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -4812,22 +4768,22 @@
     </row>
     <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -4835,22 +4791,22 @@
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -4858,22 +4814,22 @@
     </row>
     <row r="20" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -4881,22 +4837,22 @@
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -4904,22 +4860,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -4927,22 +4883,22 @@
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -4950,22 +4906,22 @@
     </row>
     <row r="24" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -4973,22 +4929,22 @@
     </row>
     <row r="25" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -4996,22 +4952,22 @@
     </row>
     <row r="26" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -5019,22 +4975,22 @@
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -5042,22 +4998,22 @@
     </row>
     <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -5068,26 +5024,26 @@
         <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29" xr:uid="{BE6CD60B-24EF-4DB9-BB5A-0C0FE4B3B915}"/>
+  <autoFilter ref="A1:G29" xr:uid="{2C9AB410-9F98-4B57-8C01-BB56273A1DB6}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85214D4E-0F42-4EFC-9550-1B087F5508EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4E5276A-73D7-4582-91CF-315637C10415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FE2258D7-CECA-4541-BD4E-C522E062856E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B789291-8918-40FE-A563-E90D4F6EDFA8}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="389">
   <si>
     <t>通番</t>
   </si>
@@ -63,40 +63,40 @@
     <t>実行（一括実行）</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>実行（実施結果取得）</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>実行（実施状況確認）</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>実行（実施結果集計）</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>実行（経年比較）</t>
+  </si>
+  <si>
+    <t>ログ</t>
+  </si>
+  <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>実行（実施結果取得）</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>実行（実施状況確認）</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>実行（実施結果集計）</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>実行（経年比較）</t>
-  </si>
-  <si>
-    <t>ログ</t>
   </si>
   <si>
     <t>環境設定（共通）</t>
@@ -152,16 +152,16 @@
     <t>「対象のグループ」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態（実施結果取得-テスト）：成功または警告
-状態（実施結果取得-アンケート）：成功または警告
-状態（実施状況確認-テスト・アンケート）：成功または警告
-状態（実施結果集計-テスト）：成功または警告
-状態（実施結果集計-アンケート）：成功または警告
+    <t>状態（実施結果取得-テスト）：成功
+状態（実施結果取得-アンケート）：成功
+状態（実施状況確認-テスト・アンケート）：成功
+状態（実施結果集計-テスト）：成功
+状態（実施結果集計-アンケート）：成功
+状態：成功
 取得結果（テスト）：nttdata-univ-material_results*.csv
 取得結果（アンケート）：nttdata-univ-class_results*.csv
 ファイル（テスト）：ok-テスト結果.xlsx
-ファイル（アンケート）：ok-アンケート結果.xlsx が作られる
-状態：成功または警告</t>
+ファイル（アンケート）：ok-アンケート結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -186,11 +186,11 @@
   </si>
   <si>
     <t>状態（実施結果取得-テスト）：スキップ
-状態（実施結果取得-アンケート）：成功または警告
-状態（実施状況確認-テスト・アンケート）：成功または警告
-状態（実施結果集計-テスト）：成功または警告
-状態（実施結果集計-アンケート）：成功または警告
-状態：成功または警告</t>
+状態（実施結果取得-アンケート）：成功
+状態（実施状況確認-テスト・アンケート）：成功
+状態（実施結果集計-テスト）：成功
+状態（実施結果集計-アンケート）：成功
+状態：成功</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -207,13 +207,13 @@
     <t>「対象のグループ」を設定した後で、「実施結果集計-投稿」にチェックを入れて、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態（実施結果取得-テスト）：成功または警告
-状態（実施結果取得-アンケート）：成功または警告
-状態（実施状況確認-テスト・アンケート）：成功または警告
-状態（実施結果集計-テスト）：成功または警告
-状態（実施結果集計-アンケート）：成功または警告
-状態（実施結果集計-投稿）：成功または警告
-状態：成功または警告</t>
+    <t>状態（実施結果取得-テスト）：成功
+状態（実施結果取得-アンケート）：成功
+状態（実施状況確認-テスト・アンケート）：成功
+状態（実施結果集計-テスト）：成功
+状態（実施結果集計-アンケート）：成功
+状態（実施結果集計-投稿）：成功
+状態：成功</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -230,14 +230,13 @@
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、すべての行の「開く」を押します。</t>
   </si>
   <si>
-    <t>開く（実施結果取得-テスト）：結果のフォルダ
-開く（実施結果取得-アンケート）：結果のフォルダ
-開く（実施状況確認-テスト・アンケート）：結果のフォルダ
-開く（実施結果集計-テスト）：結果のフォルダ
-開く（実施結果集計-アンケート）：結果のフォルダ
+    <t>開く（実施結果取得-テスト）：出力先のフォルダ
+開く（実施結果取得-アンケート）：出力先のフォルダ
+開く（実施状況確認-テスト・アンケート）：出力先のフォルダ
+開く（実施結果集計-テスト）：出力先のフォルダ
+開く（実施結果集計-アンケート）：出力先のフォルダ
 開く（実施結果集計-投稿）：投稿先のスレッド
-開く（経年比較-アンケート・テスト）：結果のフォルダ
-状態：成功または警告</t>
+開く（経年比較-アンケート・テスト）：出力先のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.1</t>
@@ -272,8 +271,8 @@
     <t>「対象のグループ」を設定した後で、「実行（テスト）」を押します。</t>
   </si>
   <si>
-    <t>状態（テスト）：成功または警告
-取得結果（テスト）：nttdata-univ-material_results*.csv が作られる</t>
+    <t>状態（テスト）：成功
+取得結果（テスト）：nttdata-univ-material_results*.csv</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -283,7 +282,7 @@
     <t>「対象のグループ」を設定した後で、「実行（テスト）」を押した後で、「開く（テスト）」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：取得した結果のフォルダ</t>
+    <t>開く：出力先のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.2</t>
@@ -292,8 +291,8 @@
     <t>「対象のグループ」を設定した後で、「実行（アンケート）」を押します。</t>
   </si>
   <si>
-    <t>状態（アンケート）：成功または警告
-取得結果（アンケート）：nttdata-univ-class_results*.csv が作られる</t>
+    <t>状態（アンケート）：成功
+取得結果（アンケート）：nttdata-univ-class_results*.csv</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -306,7 +305,7 @@
     <t>「対象のグループ」を設定した後で、「実行（取得状況確認）」を押します。</t>
   </si>
   <si>
-    <t>状態（取得状況確認）：成功または警告</t>
+    <t>状態（取得状況確認）：成功</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -337,8 +336,8 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>状態：成功または警告
-ファイル：ok-統合結果.xlsx が作られる</t>
+    <t>状態：成功
+ファイル：ok-統合結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.3
@@ -346,9 +345,6 @@
   </si>
   <si>
     <t>「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：統合結果のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.3</t>
@@ -362,29 +358,23 @@
     <t>状態：成功</t>
   </si>
   <si>
-    <t>状態（テスト）：成功または警告
-ファイル：ok-テスト結果.xlsx が作られる</t>
+    <t>状態（テスト）：成功
+ファイル：ok-テスト結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
 処理フロー：2.6</t>
   </si>
   <si>
-    <t>開いた画面：テスト集計結果のフォルダ</t>
-  </si>
-  <si>
     <t>画面設計：3.4</t>
   </si>
   <si>
-    <t>状態（アンケート）：成功または警告
-ファイル：ok-アンケート結果.xlsx が作られる</t>
+    <t>状態（アンケート）：成功
+ファイル：ok-アンケート結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
 処理フロー：2.7</t>
-  </si>
-  <si>
-    <t>開いた画面：アンケート集計結果のフォルダ</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -396,7 +386,7 @@
     <t>「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
   </si>
   <si>
-    <t>状態（投稿）：成功または警告</t>
+    <t>状態（投稿）：成功</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -406,7 +396,7 @@
     <t>「対象のグループ」を設定した後で、「実行（投稿）」を押した後で、「開く（投稿）」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：投稿先のスレッド（ブラウザ）</t>
+    <t>開く：投稿先のスレッド</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -417,8 +407,8 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>状態：成功または警告
-ファイル：ok-2026-経年比較結果.xlsx が作られる</t>
+    <t>状態：成功
+ファイル：ok-2026-経年比較結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.5
@@ -432,9 +422,6 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>開いた画面：経年比較の結果のフォルダ</t>
-  </si>
-  <si>
     <t>画面設計：3.5</t>
   </si>
   <si>
@@ -445,10 +432,6 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>状態：成功
-ファイル：ok-2026-経年比較結果.xlsx が作られる</t>
-  </si>
-  <si>
     <t>確認：いいえ</t>
   </si>
   <si>
@@ -513,7 +496,7 @@
     <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に ClientDataRootDir=saved-client-data が保存される
+    <t>設定ファイル：common.bat に saved-client-data が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1122,7 +1105,7 @@
     <t>「trackダウンロード用スクリプトのパス」の「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：（保存されている値のスクリプト名）</t>
+    <t>開く：（保存されている値のスクリプト名）</t>
   </si>
   <si>
     <t>画面設計：3.7</t>
@@ -1155,8 +1138,8 @@
   </si>
   <si>
     <t>一覧：新しいグループが追加され、選ばれる
-設定ファイル：TestCopy.bat が作られる
-Excel ファイル：TestCopy.xlsx が作られる</t>
+設定ファイル：TestCopy.bat
+Excel ファイル：TestCopy.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -1203,7 +1186,6 @@
   </si>
   <si>
     <t>設定ファイル：ok.bat に KintoneSubdomain=saved-subdomain が保存される
-画面の表示：保存後の内容に更新
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1970,7 +1952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F4C8DA-1875-4658-98AD-D64C541B8810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3FF347-E43C-4ECD-98FA-65496443BE73}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2035,10 +2017,10 @@
     </row>
     <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -2049,15 +2031,15 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
@@ -2089,14 +2071,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{C9F4C8DA-1875-4658-98AD-D64C541B8810}"/>
+  <autoFilter ref="A1:C10" xr:uid="{6D3FF347-E43C-4ECD-98FA-65496443BE73}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E235D6EC-62A0-4272-9E25-363DCBD67EC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DE1EC3-3772-457E-9757-81362616D14B}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2141,13 +2123,13 @@
         <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2164,13 +2146,13 @@
         <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2187,13 +2169,13 @@
         <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2207,16 +2189,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2224,22 +2206,22 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2256,13 +2238,13 @@
         <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2270,7 +2252,7 @@
     </row>
     <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
@@ -2279,13 +2261,13 @@
         <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -2302,13 +2284,13 @@
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -2325,27 +2307,27 @@
         <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10" xr:uid="{E235D6EC-62A0-4272-9E25-363DCBD67EC0}"/>
+  <autoFilter ref="A1:G10" xr:uid="{A2DE1EC3-3772-457E-9757-81362616D14B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{778BB135-44B1-4EAE-906E-4843AE466A61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD5630D-D91B-440D-9AE9-2A3A916BAB2C}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2473,7 +2455,7 @@
     </row>
     <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>45</v>
@@ -2495,14 +2477,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{778BB135-44B1-4EAE-906E-4843AE466A61}"/>
+  <autoFilter ref="A1:G6" xr:uid="{5FD5630D-D91B-440D-9AE9-2A3A916BAB2C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E283A024-47FC-4BF5-BA40-7D4F8D967351}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8C8349-3D3F-4CF8-B8C4-DA28AA8B9BB7}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2536,7 +2518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2582,7 +2564,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2630,7 +2612,7 @@
     </row>
     <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
@@ -2676,7 +2658,7 @@
     </row>
     <row r="8" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>45</v>
@@ -2721,14 +2703,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{E283A024-47FC-4BF5-BA40-7D4F8D967351}"/>
+  <autoFilter ref="A1:G9" xr:uid="{0E8C8349-3D3F-4CF8-B8C4-DA28AA8B9BB7}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45A692D-31CA-4754-A379-D6BB0A7EBB2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C953EF-73D3-46F5-B3DC-6FBBB49662D2}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2799,10 +2781,10 @@
         <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2816,13 +2798,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
@@ -2832,14 +2814,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{A45A692D-31CA-4754-A379-D6BB0A7EBB2C}"/>
+  <autoFilter ref="A1:G4" xr:uid="{44C953EF-73D3-46F5-B3DC-6FBBB49662D2}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A3A448-3900-44D8-8BFB-F4E0FFC7B036}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5050B890-6109-4ED1-9700-A1DF329B97DC}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2887,10 +2869,10 @@
         <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2910,10 +2892,10 @@
         <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2933,10 +2915,10 @@
         <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2956,10 +2938,10 @@
         <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2967,22 +2949,22 @@
     </row>
     <row r="6" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2996,30 +2978,30 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{47A3A448-3900-44D8-8BFB-F4E0FFC7B036}"/>
+  <autoFilter ref="A1:G7" xr:uid="{5050B890-6109-4ED1-9700-A1DF329B97DC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1892A1A-ABFC-477F-B731-E014E6D87E6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E126DC2-C4CA-4A4C-A66C-F1A4F9AE7460}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3061,16 +3043,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3084,16 +3066,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3107,30 +3089,30 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{D1892A1A-ABFC-477F-B731-E014E6D87E6E}"/>
+  <autoFilter ref="A1:G4" xr:uid="{3E126DC2-C4CA-4A4C-A66C-F1A4F9AE7460}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58010CD9-54DF-4D18-B46F-9C83DCEE22B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86C4F4A-06B6-4F37-87DF-97EF2B25DBAC}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3172,16 +3154,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3195,16 +3177,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3218,16 +3200,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3241,16 +3223,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3258,36 +3240,36 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{58010CD9-54DF-4D18-B46F-9C83DCEE22B9}"/>
+  <autoFilter ref="A1:G6" xr:uid="{A86C4F4A-06B6-4F37-87DF-97EF2B25DBAC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF28050-F508-42CF-823C-A95D2136B99B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F548FE1-E9F1-41B8-8E0D-78B4BF7F7DE6}">
   <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3321,7 +3303,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -3329,16 +3311,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3352,16 +3334,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3375,16 +3357,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3398,16 +3380,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3415,22 +3397,22 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -3444,16 +3426,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -3461,22 +3443,22 @@
     </row>
     <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -3490,16 +3472,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -3513,16 +3495,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -3530,22 +3512,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -3553,22 +3535,22 @@
     </row>
     <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -3576,22 +3558,22 @@
     </row>
     <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -3599,22 +3581,22 @@
     </row>
     <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -3622,22 +3604,22 @@
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -3645,22 +3627,22 @@
     </row>
     <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -3668,22 +3650,22 @@
     </row>
     <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -3691,22 +3673,22 @@
     </row>
     <row r="18" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -3714,22 +3696,22 @@
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -3737,22 +3719,22 @@
     </row>
     <row r="20" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -3760,22 +3742,22 @@
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -3783,22 +3765,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -3806,22 +3788,22 @@
     </row>
     <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -3829,22 +3811,22 @@
     </row>
     <row r="24" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -3852,22 +3834,22 @@
     </row>
     <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -3875,22 +3857,22 @@
     </row>
     <row r="26" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -3898,22 +3880,22 @@
     </row>
     <row r="27" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -3921,22 +3903,22 @@
     </row>
     <row r="28" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -3950,16 +3932,16 @@
         <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -3967,22 +3949,22 @@
     </row>
     <row r="30" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -3990,22 +3972,22 @@
     </row>
     <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -4013,22 +3995,22 @@
     </row>
     <row r="32" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -4036,22 +4018,22 @@
     </row>
     <row r="33" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -4059,22 +4041,22 @@
     </row>
     <row r="34" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -4082,22 +4064,22 @@
     </row>
     <row r="35" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
@@ -4105,22 +4087,22 @@
     </row>
     <row r="36" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -4128,22 +4110,22 @@
     </row>
     <row r="37" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>34</v>
@@ -4151,22 +4133,22 @@
     </row>
     <row r="38" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -4174,22 +4156,22 @@
     </row>
     <row r="39" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>34</v>
@@ -4197,22 +4179,22 @@
     </row>
     <row r="40" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>34</v>
@@ -4220,22 +4202,22 @@
     </row>
     <row r="41" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>34</v>
@@ -4243,22 +4225,22 @@
     </row>
     <row r="42" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>34</v>
@@ -4266,22 +4248,22 @@
     </row>
     <row r="43" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>34</v>
@@ -4289,22 +4271,22 @@
     </row>
     <row r="44" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>34</v>
@@ -4312,22 +4294,22 @@
     </row>
     <row r="45" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>34</v>
@@ -4341,30 +4323,30 @@
         <v>29</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>283</v>
-      </c>
       <c r="G46" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G46" xr:uid="{7BF28050-F508-42CF-823C-A95D2136B99B}"/>
+  <autoFilter ref="A1:G46" xr:uid="{7F548FE1-E9F1-41B8-8E0D-78B4BF7F7DE6}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9AB410-9F98-4B57-8C01-BB56273A1DB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C5A435-FB25-443C-A11C-42DE057E4328}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4406,16 +4388,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -4429,16 +4411,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -4452,16 +4434,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -4475,39 +4457,39 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -4521,16 +4503,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -4538,22 +4520,22 @@
     </row>
     <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -4567,16 +4549,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -4590,16 +4572,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -4607,22 +4589,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -4630,22 +4612,22 @@
     </row>
     <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -4653,22 +4635,22 @@
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -4676,22 +4658,22 @@
     </row>
     <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -4699,22 +4681,22 @@
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -4722,22 +4704,22 @@
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -4745,22 +4727,22 @@
     </row>
     <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -4768,22 +4750,22 @@
     </row>
     <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -4791,22 +4773,22 @@
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -4814,22 +4796,22 @@
     </row>
     <row r="20" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -4837,22 +4819,22 @@
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -4860,22 +4842,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -4883,22 +4865,22 @@
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -4906,22 +4888,22 @@
     </row>
     <row r="24" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -4929,22 +4911,22 @@
     </row>
     <row r="25" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -4952,22 +4934,22 @@
     </row>
     <row r="26" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -4975,22 +4957,22 @@
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -4998,22 +4980,22 @@
     </row>
     <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -5027,23 +5009,23 @@
         <v>45</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29" xr:uid="{2C9AB410-9F98-4B57-8C01-BB56273A1DB6}"/>
+  <autoFilter ref="A1:G29" xr:uid="{F3C5A435-FB25-443C-A11C-42DE057E4328}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4E5276A-73D7-4582-91CF-315637C10415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{756B8F48-7514-4D3B-A3CB-3D7E830C3C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B789291-8918-40FE-A563-E90D4F6EDFA8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B1179AAD-0FE1-426D-8094-17FEECE22F83}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（実施結果集計）'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（経年比較）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="387">
   <si>
     <t>通番</t>
   </si>
@@ -102,7 +102,7 @@
     <t>環境設定（共通）</t>
   </si>
   <si>
-    <t>45</t>
+    <t>44</t>
   </si>
   <si>
     <t>環境設定（グループ別）</t>
@@ -160,8 +160,8 @@
 状態：成功
 取得結果（テスト）：nttdata-univ-material_results*.csv
 取得結果（アンケート）：nttdata-univ-class_results*.csv
-ファイル（テスト）：ok-テスト結果.xlsx
-ファイル（アンケート）：ok-アンケート結果.xlsx</t>
+集計結果（テスト）：ok-テスト結果.xlsx
+集計結果（アンケート）：ok-アンケート結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -337,7 +337,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：ok-統合結果.xlsx</t>
+集計結果：ok-統合結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.3
@@ -359,7 +359,7 @@
   </si>
   <si>
     <t>状態（テスト）：成功
-ファイル：ok-テスト結果.xlsx</t>
+集計結果：ok-テスト結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -370,7 +370,7 @@
   </si>
   <si>
     <t>状態（アンケート）：成功
-ファイル：ok-アンケート結果.xlsx</t>
+集計結果：ok-アンケート結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -408,7 +408,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：ok-2026-経年比較結果.xlsx</t>
+集計結果：ok-2026-経年比較結果.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.5
@@ -432,6 +432,10 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
+    <t>状態：成功
+ファイル：ok-2026-経年比較結果.xlsx</t>
+  </si>
+  <si>
     <t>確認：いいえ</t>
   </si>
   <si>
@@ -496,7 +500,7 @@
     <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-client-data が保存される
+    <t>設定ファイル：common.bat に ClientDataRootDir=saved-client-data が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1090,16 +1094,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>入力なし</t>
-  </si>
-  <si>
-    <t>「再読込」を押します。</t>
-  </si>
-  <si>
-    <t>状態（再読込）：完了</t>
+    <t>なし</t>
   </si>
   <si>
     <t>「trackダウンロード用スクリプトのパス」の「開く」を押します。</t>
@@ -1212,14 +1207,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-ログイン名：テスト用の値
+ログイン名：saved-login-name
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+    <t>設定ファイル：ok.bat に KintoneLoginName=saved-login-name が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1237,14 +1232,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-パスワード：テスト用の値
+パスワード：saved-pass
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintonePassword が保存される
+    <t>設定ファイル：ok.bat に KintonePassword=saved-pass が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1952,7 +1947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3FF347-E43C-4ECD-98FA-65496443BE73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AAA2B8A-55D9-47EF-A9D6-AA44EF88288F}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2071,14 +2066,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{6D3FF347-E43C-4ECD-98FA-65496443BE73}"/>
+  <autoFilter ref="A1:C10" xr:uid="{5AAA2B8A-55D9-47EF-A9D6-AA44EF88288F}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2DE1EC3-3772-457E-9757-81362616D14B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE7ACE0-30B0-485B-938E-8B97C38E9190}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2123,13 +2118,13 @@
         <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2146,13 +2141,13 @@
         <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2169,13 +2164,13 @@
         <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2189,16 +2184,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2212,16 +2207,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2238,13 +2233,13 @@
         <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2261,13 +2256,13 @@
         <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -2284,13 +2279,13 @@
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -2307,27 +2302,27 @@
         <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>367</v>
-      </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10" xr:uid="{A2DE1EC3-3772-457E-9757-81362616D14B}"/>
+  <autoFilter ref="A1:G10" xr:uid="{CFE7ACE0-30B0-485B-938E-8B97C38E9190}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD5630D-D91B-440D-9AE9-2A3A916BAB2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB5579DD-652E-4F8E-A40A-8CD9574FE698}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2477,14 +2472,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{5FD5630D-D91B-440D-9AE9-2A3A916BAB2C}"/>
+  <autoFilter ref="A1:G6" xr:uid="{AB5579DD-652E-4F8E-A40A-8CD9574FE698}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8C8349-3D3F-4CF8-B8C4-DA28AA8B9BB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788E2911-9756-4BCE-808D-1546DC52ECA6}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2703,14 +2698,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{0E8C8349-3D3F-4CF8-B8C4-DA28AA8B9BB7}"/>
+  <autoFilter ref="A1:G9" xr:uid="{788E2911-9756-4BCE-808D-1546DC52ECA6}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C953EF-73D3-46F5-B3DC-6FBBB49662D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD453FAF-C088-4529-915E-A0047083C3A8}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2814,14 +2809,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{44C953EF-73D3-46F5-B3DC-6FBBB49662D2}"/>
+  <autoFilter ref="A1:G4" xr:uid="{AD453FAF-C088-4529-915E-A0047083C3A8}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5050B890-6109-4ED1-9700-A1DF329B97DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0F407E-486C-4959-8431-25A0E84211F9}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2994,14 +2989,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{5050B890-6109-4ED1-9700-A1DF329B97DC}"/>
+  <autoFilter ref="A1:G7" xr:uid="{3E0F407E-486C-4959-8431-25A0E84211F9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E126DC2-C4CA-4A4C-A66C-F1A4F9AE7460}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBBA4FA9-9CDB-4AE6-999F-24B463D6C651}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3095,7 +3090,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -3105,14 +3100,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{3E126DC2-C4CA-4A4C-A66C-F1A4F9AE7460}"/>
+  <autoFilter ref="A1:G4" xr:uid="{EBBA4FA9-9CDB-4AE6-999F-24B463D6C651}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86C4F4A-06B6-4F37-87DF-97EF2B25DBAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8060DF-ACB7-44C7-8FC7-41996CCC80DF}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3154,16 +3149,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3177,16 +3172,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3200,16 +3195,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3223,16 +3218,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3246,31 +3241,31 @@
         <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{A86C4F4A-06B6-4F37-87DF-97EF2B25DBAC}"/>
+  <autoFilter ref="A1:G6" xr:uid="{DF8060DF-ACB7-44C7-8FC7-41996CCC80DF}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F548FE1-E9F1-41B8-8E0D-78B4BF7F7DE6}">
-  <dimension ref="A1:G46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71668746-28F1-4878-BB08-B67702B6BC1D}">
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -3303,7 +3298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -3311,16 +3306,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3334,16 +3329,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3357,16 +3352,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3380,16 +3375,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3403,16 +3398,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -3426,16 +3421,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -3449,16 +3444,16 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -3472,16 +3467,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -3495,16 +3490,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -3512,22 +3507,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -3535,22 +3530,22 @@
     </row>
     <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -3558,22 +3553,22 @@
     </row>
     <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -3581,22 +3576,22 @@
     </row>
     <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -3604,22 +3599,22 @@
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -3627,22 +3622,22 @@
     </row>
     <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -3650,22 +3645,22 @@
     </row>
     <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -3673,22 +3668,22 @@
     </row>
     <row r="18" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -3696,22 +3691,22 @@
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -3719,22 +3714,22 @@
     </row>
     <row r="20" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -3742,22 +3737,22 @@
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -3765,22 +3760,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -3788,22 +3783,22 @@
     </row>
     <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -3811,22 +3806,22 @@
     </row>
     <row r="24" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -3834,22 +3829,22 @@
     </row>
     <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -3857,22 +3852,22 @@
     </row>
     <row r="26" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -3880,22 +3875,22 @@
     </row>
     <row r="27" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -3903,22 +3898,22 @@
     </row>
     <row r="28" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -3932,16 +3927,16 @@
         <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -3949,22 +3944,22 @@
     </row>
     <row r="30" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -3972,22 +3967,22 @@
     </row>
     <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -3995,22 +3990,22 @@
     </row>
     <row r="32" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -4018,22 +4013,22 @@
     </row>
     <row r="33" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -4041,22 +4036,22 @@
     </row>
     <row r="34" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -4064,22 +4059,22 @@
     </row>
     <row r="35" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
@@ -4087,22 +4082,22 @@
     </row>
     <row r="36" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -4110,22 +4105,22 @@
     </row>
     <row r="37" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>34</v>
@@ -4133,22 +4128,22 @@
     </row>
     <row r="38" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -4156,22 +4151,22 @@
     </row>
     <row r="39" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>34</v>
@@ -4179,22 +4174,22 @@
     </row>
     <row r="40" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>34</v>
@@ -4202,22 +4197,22 @@
     </row>
     <row r="41" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>34</v>
@@ -4225,22 +4220,22 @@
     </row>
     <row r="42" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>34</v>
@@ -4248,22 +4243,22 @@
     </row>
     <row r="43" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>34</v>
@@ -4271,30 +4266,30 @@
     </row>
     <row r="44" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>29</v>
@@ -4309,44 +4304,21 @@
         <v>275</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>115</v>
+        <v>276</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="144" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G46" xr:uid="{7F548FE1-E9F1-41B8-8E0D-78B4BF7F7DE6}"/>
+  <autoFilter ref="A1:G45" xr:uid="{71668746-28F1-4878-BB08-B67702B6BC1D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C5A435-FB25-443C-A11C-42DE057E4328}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1A200D-15CB-4C9F-807D-E50DC2A2F5D9}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4388,16 +4360,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -4411,16 +4383,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -4434,16 +4406,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -4457,16 +4429,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -4480,16 +4452,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -4503,22 +4475,22 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -4526,16 +4498,16 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -4549,22 +4521,22 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -4572,16 +4544,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -4589,22 +4561,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>314</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -4612,22 +4584,22 @@
     </row>
     <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -4635,22 +4607,22 @@
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -4658,22 +4630,22 @@
     </row>
     <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -4681,22 +4653,22 @@
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -4704,22 +4676,22 @@
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -4727,22 +4699,22 @@
     </row>
     <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -4750,22 +4722,22 @@
     </row>
     <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -4773,22 +4745,22 @@
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -4796,22 +4768,22 @@
     </row>
     <row r="20" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -4819,22 +4791,22 @@
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -4842,22 +4814,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -4865,22 +4837,22 @@
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -4888,22 +4860,22 @@
     </row>
     <row r="24" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -4911,22 +4883,22 @@
     </row>
     <row r="25" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -4934,22 +4906,22 @@
     </row>
     <row r="26" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -4957,22 +4929,22 @@
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -4980,22 +4952,22 @@
     </row>
     <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -5009,23 +4981,23 @@
         <v>45</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29" xr:uid="{F3C5A435-FB25-443C-A11C-42DE057E4328}"/>
+  <autoFilter ref="A1:G29" xr:uid="{2F1A200D-15CB-4C9F-807D-E50DC2A2F5D9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/track-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\track-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{756B8F48-7514-4D3B-A3CB-3D7E830C3C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A522CF8C-E96A-4EA7-899B-F7CE17A8005C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B1179AAD-0FE1-426D-8094-17FEECE22F83}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5166F7AE-D4F8-45F2-AC94-239ED35D82AB}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="412">
   <si>
     <t>通番</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>環境設定（マスター）</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>区分</t>
@@ -793,9 +796,6 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>統合結果の出力先：saved-output-combine
 設定ファイル：common.bat</t>
   </si>
@@ -1464,6 +1464,11 @@
 状態（ユーザー）：失敗</t>
   </si>
   <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
     <t>「対象のグループ」を設定した後で、「同期実行」を押します。</t>
   </si>
   <si>
@@ -1474,74 +1479,185 @@
 処理フロー：2.22</t>
   </si>
   <si>
-    <t>「対象のグループ」を設定した後で、テストの表で「追加（テスト）」を押します。</t>
-  </si>
-  <si>
-    <t>表：末尾に空の行が追加される（未確認）</t>
-  </si>
-  <si>
-    <t>画面設計：3.9
-処理フロー：2.24</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、テストの表の1行目の「削除（テスト）」を押します。</t>
+    <t>「対象のグループ」を設定した後で、「追加（テスト）」を押します。</t>
+  </si>
+  <si>
+    <t>テストの通番（2行目）：2
+テストのテスト名（2行目）：空</t>
+  </si>
+  <si>
+    <t>画面設計：3.9</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「削除（テストの1行目）」を押します。</t>
   </si>
   <si>
     <t>表：その行が削除される</t>
   </si>
   <si>
-    <t>画面設計：3.9
-処理フロー：2.23</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
-テスト名（1行目）：saved-subject
-設定ファイル：ok.bat</t>
+テスト名（1行目）：saved-test-name
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
   </si>
   <si>
     <t>「対象のグループ」と「テスト名（1行目）」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>テスト名（1行目）：saved-subject が表示される
+    <t>テストのテスト名（1行目）：saved-test-name が表示される
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>画面設計：3.9
-処理フロー：2.20</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
-テスト名：tmp-reload
-設定ファイル：ok.bat</t>
+TrackId（1行目）：saved-track-id
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「TrackId（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>テストのTrackId（1行目）：saved-track-id が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+DL（1行目）：FALSE
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「DL（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>テストのDL（1行目）：FALSE が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+停止中（1行目）：TRUE
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「停止中（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>テストの停止中（1行目）：TRUE が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+テスト名（1行目）：tmp-reload
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
   </si>
   <si>
     <t>「対象のグループ」と「テスト名（1行目）」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>テスト名（1行目）：（保存されている値）
+    <t>テストのテスト名（1行目）：（保存されている値）
 変えた内容：消える
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>画面設計：3.9
-処理フロー：2.21</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、アンケートの表で「追加（アンケート）」を押します。</t>
-  </si>
-  <si>
-    <t>画面設計：3.9
-処理フロー：2.26</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、アンケートの表の2行目の「削除（アンケート）」を押します。</t>
-  </si>
-  <si>
-    <t>表：2行目（48693-639607）が削除される</t>
-  </si>
-  <si>
-    <t>画面設計：3.9
-処理フロー：2.25</t>
+    <t>対象のグループ：ok
+TrackId（1行目）：tmp-reload
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「TrackId（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テストのTrackId（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「DL（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テストのDL（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「停止中（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テストの停止中（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「追加（アンケート）」を押します。</t>
+  </si>
+  <si>
+    <t>アンケートの通番（2行目）：2
+アンケートのアンケート名（2行目）：空</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「削除（アンケートの1行目）」を押します。</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+アンケート名（1行目）：saved-survey-name
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「アンケート名（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>アンケートのアンケート名（1行目）：saved-survey-name が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>アンケートのTrackId（1行目）：saved-track-id が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>アンケートのDL（1行目）：FALSE が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>アンケートの停止中（1行目）：TRUE が表示される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+アンケート名（1行目）：tmp-reload
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「アンケート名（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>アンケートのアンケート名（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>アンケートのTrackId（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>アンケートのDL（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>アンケートの停止中（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+設定ファイル：ng.bat
+Excel ファイル：ng.xlsx</t>
   </si>
   <si>
     <t>状態（同期実行）：失敗</t>
@@ -1947,7 +2063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AAA2B8A-55D9-47EF-A9D6-AA44EF88288F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0482F497-F783-4B6B-AB4E-0836BD6565E8}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2062,19 +2178,19 @@
         <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{5AAA2B8A-55D9-47EF-A9D6-AA44EF88288F}"/>
+  <autoFilter ref="A1:C10" xr:uid="{0482F497-F783-4B6B-AB4E-0836BD6565E8}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE7ACE0-30B0-485B-938E-8B97C38E9190}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA6EAF4-EA3A-4CA8-B227-5C87C4A61293}">
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -2089,99 +2205,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>372</v>
@@ -2193,67 +2309,67 @@
         <v>374</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>378</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>367</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>381</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>382</v>
@@ -2262,67 +2378,389 @@
         <v>383</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>384</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>387</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>34</v>
+      <c r="D13" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10" xr:uid="{CFE7ACE0-30B0-485B-938E-8B97C38E9190}"/>
+  <autoFilter ref="A1:G24" xr:uid="{2BA6EAF4-EA3A-4CA8-B227-5C87C4A61293}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB5579DD-652E-4F8E-A40A-8CD9574FE698}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3157B2-742C-4866-87A5-C16CB2F45627}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2338,22 +2776,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -2361,22 +2799,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -2384,22 +2822,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -2407,22 +2845,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -2430,22 +2868,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -2453,33 +2891,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{AB5579DD-652E-4F8E-A40A-8CD9574FE698}"/>
+  <autoFilter ref="A1:G6" xr:uid="{EF3157B2-742C-4866-87A5-C16CB2F45627}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788E2911-9756-4BCE-808D-1546DC52ECA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA55EA7-3F9C-4071-A36A-484404FEB955}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2495,22 +2933,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -2518,22 +2956,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -2541,22 +2979,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -2564,22 +3002,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -2587,22 +3025,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -2610,22 +3048,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -2633,22 +3071,22 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="162" x14ac:dyDescent="0.45">
@@ -2656,22 +3094,22 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -2679,33 +3117,33 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{788E2911-9756-4BCE-808D-1546DC52ECA6}"/>
+  <autoFilter ref="A1:G9" xr:uid="{0BA55EA7-3F9C-4071-A36A-484404FEB955}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD453FAF-C088-4529-915E-A0047083C3A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A2FACFF-178D-4478-AD68-A238FA746B08}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2721,22 +3159,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -2744,22 +3182,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -2767,22 +3205,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
@@ -2790,33 +3228,33 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{AD453FAF-C088-4529-915E-A0047083C3A8}"/>
+  <autoFilter ref="A1:G4" xr:uid="{3A2FACFF-178D-4478-AD68-A238FA746B08}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0F407E-486C-4959-8431-25A0E84211F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B08B1E4-8D1F-4D03-A9CB-6A0425E3C7B5}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2832,22 +3270,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -2855,22 +3293,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -2878,22 +3316,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -2901,22 +3339,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -2924,22 +3362,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="342" x14ac:dyDescent="0.45">
@@ -2947,22 +3385,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="342" x14ac:dyDescent="0.45">
@@ -2970,33 +3408,33 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{3E0F407E-486C-4959-8431-25A0E84211F9}"/>
+  <autoFilter ref="A1:G7" xr:uid="{9B08B1E4-8D1F-4D03-A9CB-6A0425E3C7B5}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBBA4FA9-9CDB-4AE6-999F-24B463D6C651}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{481500AC-A58A-48CC-84BC-0665A6E7D27E}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3012,22 +3450,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -3035,22 +3473,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -3058,22 +3496,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -3081,33 +3519,33 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{EBBA4FA9-9CDB-4AE6-999F-24B463D6C651}"/>
+  <autoFilter ref="A1:G4" xr:uid="{481500AC-A58A-48CC-84BC-0665A6E7D27E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8060DF-ACB7-44C7-8FC7-41996CCC80DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684723A3-C4E2-4D6F-A54B-6C0D4998ABBC}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3123,22 +3561,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3146,22 +3584,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -3169,22 +3607,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3192,22 +3630,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -3215,22 +3653,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3238,33 +3676,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{DF8060DF-ACB7-44C7-8FC7-41996CCC80DF}"/>
+  <autoFilter ref="A1:G6" xr:uid="{684723A3-C4E2-4D6F-A54B-6C0D4998ABBC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71668746-28F1-4878-BB08-B67702B6BC1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0EDBBC-8654-4EE4-A5BB-483BD297C8B8}">
   <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3280,22 +3718,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3303,22 +3741,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3326,22 +3764,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3349,22 +3787,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3372,22 +3810,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3395,22 +3833,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3418,22 +3856,22 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3441,22 +3879,22 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3464,22 +3902,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3487,329 +3925,329 @@
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>191</v>
@@ -3821,10 +4259,10 @@
         <v>193</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3832,7 +4270,7 @@
         <v>194</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>195</v>
@@ -3844,10 +4282,10 @@
         <v>197</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="288" x14ac:dyDescent="0.45">
@@ -3855,7 +4293,7 @@
         <v>198</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>199</v>
@@ -3867,10 +4305,10 @@
         <v>201</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3878,7 +4316,7 @@
         <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>203</v>
@@ -3890,10 +4328,10 @@
         <v>205</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="288" x14ac:dyDescent="0.45">
@@ -3901,7 +4339,7 @@
         <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>207</v>
@@ -3913,10 +4351,10 @@
         <v>209</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3924,7 +4362,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>210</v>
@@ -3936,10 +4374,10 @@
         <v>212</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="288" x14ac:dyDescent="0.45">
@@ -3947,7 +4385,7 @@
         <v>213</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>214</v>
@@ -3959,10 +4397,10 @@
         <v>216</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3970,7 +4408,7 @@
         <v>217</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>218</v>
@@ -3982,10 +4420,10 @@
         <v>220</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3993,7 +4431,7 @@
         <v>221</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>222</v>
@@ -4005,10 +4443,10 @@
         <v>224</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -4016,7 +4454,7 @@
         <v>225</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>226</v>
@@ -4028,10 +4466,10 @@
         <v>228</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -4039,7 +4477,7 @@
         <v>229</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>230</v>
@@ -4051,10 +4489,10 @@
         <v>232</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -4062,7 +4500,7 @@
         <v>233</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>234</v>
@@ -4074,10 +4512,10 @@
         <v>236</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -4085,7 +4523,7 @@
         <v>237</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>238</v>
@@ -4097,10 +4535,10 @@
         <v>240</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -4108,7 +4546,7 @@
         <v>241</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>242</v>
@@ -4120,10 +4558,10 @@
         <v>244</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -4131,7 +4569,7 @@
         <v>245</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>246</v>
@@ -4143,10 +4581,10 @@
         <v>248</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4154,7 +4592,7 @@
         <v>249</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>250</v>
@@ -4166,10 +4604,10 @@
         <v>252</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4177,7 +4615,7 @@
         <v>253</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>254</v>
@@ -4189,10 +4627,10 @@
         <v>256</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4200,7 +4638,7 @@
         <v>257</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>258</v>
@@ -4212,10 +4650,10 @@
         <v>260</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -4223,7 +4661,7 @@
         <v>261</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>262</v>
@@ -4235,10 +4673,10 @@
         <v>264</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4246,7 +4684,7 @@
         <v>265</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>266</v>
@@ -4258,10 +4696,10 @@
         <v>268</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -4269,7 +4707,7 @@
         <v>269</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>270</v>
@@ -4281,10 +4719,10 @@
         <v>272</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="144" x14ac:dyDescent="0.45">
@@ -4292,7 +4730,7 @@
         <v>18</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>273</v>
@@ -4307,18 +4745,18 @@
         <v>276</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G45" xr:uid="{71668746-28F1-4878-BB08-B67702B6BC1D}"/>
+  <autoFilter ref="A1:G45" xr:uid="{1C0EDBBC-8654-4EE4-A5BB-483BD297C8B8}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1A200D-15CB-4C9F-807D-E50DC2A2F5D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E62622D-6879-4BA2-A3C5-7B93B305D422}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4334,22 +4772,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4357,7 +4795,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>277</v>
@@ -4372,7 +4810,7 @@
         <v>280</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -4380,7 +4818,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>281</v>
@@ -4395,7 +4833,7 @@
         <v>284</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -4403,7 +4841,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>285</v>
@@ -4418,7 +4856,7 @@
         <v>288</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -4426,7 +4864,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>289</v>
@@ -4441,7 +4879,7 @@
         <v>292</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4449,7 +4887,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>293</v>
@@ -4464,7 +4902,7 @@
         <v>296</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -4472,7 +4910,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>297</v>
@@ -4487,7 +4925,7 @@
         <v>300</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4495,7 +4933,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>301</v>
@@ -4510,7 +4948,7 @@
         <v>296</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -4518,7 +4956,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>304</v>
@@ -4533,7 +4971,7 @@
         <v>288</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -4541,7 +4979,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>307</v>
@@ -4556,15 +4994,15 @@
         <v>296</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>310</v>
@@ -4579,15 +5017,15 @@
         <v>296</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>313</v>
@@ -4602,15 +5040,15 @@
         <v>288</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>316</v>
@@ -4625,15 +5063,15 @@
         <v>296</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>319</v>
@@ -4648,15 +5086,15 @@
         <v>288</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>322</v>
@@ -4671,15 +5109,15 @@
         <v>296</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>325</v>
@@ -4694,15 +5132,15 @@
         <v>288</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>328</v>
@@ -4717,15 +5155,15 @@
         <v>331</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>332</v>
@@ -4740,15 +5178,15 @@
         <v>296</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>335</v>
@@ -4763,15 +5201,15 @@
         <v>288</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>338</v>
@@ -4786,15 +5224,15 @@
         <v>296</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>341</v>
@@ -4809,15 +5247,15 @@
         <v>288</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>344</v>
@@ -4832,15 +5270,15 @@
         <v>280</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>346</v>
@@ -4855,15 +5293,15 @@
         <v>280</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>349</v>
@@ -4878,7 +5316,7 @@
         <v>284</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4886,7 +5324,7 @@
         <v>194</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>344</v>
@@ -4901,7 +5339,7 @@
         <v>284</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -4909,7 +5347,7 @@
         <v>198</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>352</v>
@@ -4924,7 +5362,7 @@
         <v>288</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4932,7 +5370,7 @@
         <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>355</v>
@@ -4947,7 +5385,7 @@
         <v>288</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4955,7 +5393,7 @@
         <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>358</v>
@@ -4970,7 +5408,7 @@
         <v>292</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4978,7 +5416,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>360</v>
@@ -4993,11 +5431,11 @@
         <v>331</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29" xr:uid="{2F1A200D-15CB-4C9F-807D-E50DC2A2F5D9}"/>
+  <autoFilter ref="A1:G29" xr:uid="{6E62622D-6879-4BA2-A3C5-7B93B305D422}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
